--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -249,6 +250,9 @@
       <name val="Microsoft YaHei"/>
       <color rgb="0078716C"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -784,7 +788,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -828,6 +832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3840,6 +3845,1305 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" s="19" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>360</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="n">
+        <v>300</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>高强度训练</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>480</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>脚踝有一点不舒服 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" t="n">
+        <v>360</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" t="n">
+        <v>360</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
+        <v>360</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J9" t="n">
+        <v>300</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>酸痛未填</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" t="n">
+        <v>360</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>左膝盖 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" t="n">
+        <v>360</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" t="n">
+        <v>300</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" t="n">
+        <v>360</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" t="n">
+        <v>360</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" t="n">
+        <v>360</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>脚掌骨疼 ⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" t="n">
+        <v>360</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" t="n">
+        <v>360</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" t="n">
+        <v>360</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>420</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>轻量训练</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>125</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>轻量训练</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>45</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>发烧 🔴 仅热身+抢圈→退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>60</v>
+      </c>
+      <c r="J23" t="n">
+        <v>360</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>420</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J25" t="n">
+        <v>360</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>高强度训练</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" t="n">
+        <v>480</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>轻量训练</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" t="n">
+        <v>75</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>刘子结</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>轻量训练</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>试训·仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>轻量训练</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>25</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>试训·仅热身+抢圈+转换→未参加比赛</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7/15 训练日 · 27人参训 · 总sRPE≈8345 · 均RPE≈53.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>红旗: 朱云天发烧🔴 巫林峰脚掌骨疼⚠️ 张俊哲脚踝⚠️ 王捷左膝⚠️</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8687,7 +9991,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -12031,13 +13334,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/8-7/14)</t>
+          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/9-7/15)</t>
         </is>
       </c>
     </row>
@@ -12116,6 +13419,11 @@
           <t>7/14</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12129,10 +13437,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1790</v>
+        <v>2090</v>
       </c>
       <c r="D4" t="n">
-        <v>255.7</v>
+        <v>298.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -12162,6 +13470,9 @@
       <c r="M4" t="n">
         <v>300</v>
       </c>
+      <c r="N4" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12175,10 +13486,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1035</v>
+        <v>1170</v>
       </c>
       <c r="D5" t="n">
-        <v>147.9</v>
+        <v>167.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -12208,6 +13519,9 @@
       <c r="M5" t="n">
         <v>240</v>
       </c>
+      <c r="N5" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12221,10 +13535,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>795</v>
+        <v>870</v>
       </c>
       <c r="D6" t="n">
-        <v>113.6</v>
+        <v>124.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -12254,6 +13568,9 @@
       <c r="M6" t="n">
         <v>180</v>
       </c>
+      <c r="N6" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12267,10 +13584,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1875</v>
+        <v>2295</v>
       </c>
       <c r="D7" t="n">
-        <v>267.9</v>
+        <v>327.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -12300,6 +13617,9 @@
       <c r="M7" t="n">
         <v>240</v>
       </c>
+      <c r="N7" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12313,10 +13633,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1734</v>
+        <v>2034</v>
       </c>
       <c r="D8" t="n">
-        <v>247.7</v>
+        <v>290.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -12346,6 +13666,9 @@
       <c r="M8" t="n">
         <v>180</v>
       </c>
+      <c r="N8" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12359,10 +13682,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>875</v>
+        <v>1010</v>
       </c>
       <c r="D9" t="n">
-        <v>125</v>
+        <v>144.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -12392,6 +13715,9 @@
       <c r="M9" t="n">
         <v>180</v>
       </c>
+      <c r="N9" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12405,10 +13731,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>960</v>
+        <v>1035</v>
       </c>
       <c r="D10" t="n">
-        <v>137.1</v>
+        <v>147.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -12438,6 +13764,9 @@
       <c r="M10" t="n">
         <v>180</v>
       </c>
+      <c r="N10" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12451,10 +13780,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1759</v>
+        <v>2059</v>
       </c>
       <c r="D11" t="n">
-        <v>251.3</v>
+        <v>294.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -12484,6 +13813,9 @@
       <c r="M11" t="n">
         <v>240</v>
       </c>
+      <c r="N11" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12497,10 +13829,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1880</v>
+        <v>2180</v>
       </c>
       <c r="D12" t="n">
-        <v>268.6</v>
+        <v>311.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -12530,6 +13862,9 @@
       <c r="M12" t="n">
         <v>240</v>
       </c>
+      <c r="N12" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12543,10 +13878,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>535</v>
+        <v>670</v>
       </c>
       <c r="D13" t="n">
-        <v>76.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -12567,6 +13902,9 @@
       <c r="M13" t="n">
         <v>240</v>
       </c>
+      <c r="N13" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12580,10 +13918,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1152</v>
+        <v>1287</v>
       </c>
       <c r="D14" t="n">
-        <v>164.6</v>
+        <v>183.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -12613,6 +13951,9 @@
       <c r="M14" t="n">
         <v>300</v>
       </c>
+      <c r="N14" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12626,10 +13967,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1625</v>
+        <v>1925</v>
       </c>
       <c r="D15" t="n">
-        <v>232.1</v>
+        <v>275</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -12659,6 +14000,9 @@
       <c r="M15" t="n">
         <v>180</v>
       </c>
+      <c r="N15" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12672,10 +14016,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1795</v>
+        <v>2095</v>
       </c>
       <c r="D16" t="n">
-        <v>256.4</v>
+        <v>299.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -12705,6 +14049,9 @@
       <c r="M16" t="n">
         <v>240</v>
       </c>
+      <c r="N16" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12718,10 +14065,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>785</v>
+        <v>920</v>
       </c>
       <c r="D17" t="n">
-        <v>112.1</v>
+        <v>131.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -12751,6 +14098,9 @@
       <c r="M17" t="n">
         <v>120</v>
       </c>
+      <c r="N17" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12764,10 +14114,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>735</v>
+        <v>870</v>
       </c>
       <c r="D18" t="n">
-        <v>105</v>
+        <v>124.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -12797,6 +14147,9 @@
       <c r="M18" t="n">
         <v>120</v>
       </c>
+      <c r="N18" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12810,10 +14163,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>795</v>
+        <v>990</v>
       </c>
       <c r="D19" t="n">
-        <v>113.6</v>
+        <v>141.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -12843,6 +14196,9 @@
       <c r="M19" t="n">
         <v>120</v>
       </c>
+      <c r="N19" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12856,10 +14212,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>535</v>
+        <v>355</v>
       </c>
       <c r="D20" t="n">
-        <v>76.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -12880,6 +14236,9 @@
       <c r="M20" t="n">
         <v>240</v>
       </c>
+      <c r="N20" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12893,10 +14252,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>515</v>
+        <v>415</v>
       </c>
       <c r="D21" t="n">
-        <v>73.59999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -12920,6 +14279,9 @@
       <c r="M21" t="n">
         <v>120</v>
       </c>
+      <c r="N21" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12933,10 +14295,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1445</v>
+        <v>1745</v>
       </c>
       <c r="D22" t="n">
-        <v>206.4</v>
+        <v>249.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -12966,6 +14328,9 @@
       <c r="M22" t="n">
         <v>180</v>
       </c>
+      <c r="N22" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12979,10 +14344,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1955</v>
+        <v>2315</v>
       </c>
       <c r="D23" t="n">
-        <v>279.3</v>
+        <v>330.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -13012,6 +14377,9 @@
       <c r="M23" t="n">
         <v>180</v>
       </c>
+      <c r="N23" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13025,10 +14393,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1920</v>
+        <v>2220</v>
       </c>
       <c r="D24" t="n">
-        <v>274.3</v>
+        <v>317.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -13058,6 +14426,9 @@
       <c r="M24" t="n">
         <v>180</v>
       </c>
+      <c r="N24" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13071,10 +14442,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>772</v>
+        <v>1027</v>
       </c>
       <c r="D25" t="n">
-        <v>110.3</v>
+        <v>146.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -13104,6 +14475,9 @@
       <c r="M25" t="n">
         <v>120</v>
       </c>
+      <c r="N25" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13117,10 +14491,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>590</v>
+        <v>440</v>
       </c>
       <c r="D26" t="n">
-        <v>84.3</v>
+        <v>62.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -13150,6 +14524,9 @@
       <c r="M26" t="n">
         <v>60</v>
       </c>
+      <c r="N26" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13163,10 +14540,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1131</v>
+        <v>1431</v>
       </c>
       <c r="D27" t="n">
-        <v>161.6</v>
+        <v>204.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -13187,6 +14564,9 @@
       <c r="I27" t="n">
         <v>711</v>
       </c>
+      <c r="N27" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13200,10 +14580,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>405</v>
+        <v>480</v>
       </c>
       <c r="D28" t="n">
-        <v>57.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -13221,6 +14601,9 @@
       <c r="H28" t="n">
         <v>180</v>
       </c>
+      <c r="N28" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13249,6 +14632,9 @@
           <t>📊 数据不足</t>
         </is>
       </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13276,6 +14662,9 @@
         <is>
           <t>📊 数据不足</t>
         </is>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕（未填晨间）</t>
+          <t>已签约·正式入队🆕</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>睡眠未填</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕（未填晨间）</t>
+          <t>已签约·正式入队🆕</t>
         </is>
       </c>
     </row>
@@ -6253,10 +6253,11 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7/17 行程日·赴大连(7/19客场vs大连英博B) · 26人填晨间问卷 · 无训练 · 名单29人(三签约🆕)</t>
+          <t>7/17 行程日·赴大连(7/19客场vs大连英博B) · 28人填晨间问卷 · 无训练 · 名单29人(三签约🆕)</t>
         </is>
       </c>
     </row>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -249,6 +250,9 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -785,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -819,6 +823,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1232,7 +1237,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1254,6 +1259,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -2511,7 +2517,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -3790,6 +3796,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -5122,6 +5129,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -5148,7 +5156,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -6279,8 +6287,1318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>55</v>
+      </c>
+      <c r="J2" t="n">
+        <v>110</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>脚踝痛·第4天</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J3" t="n">
+        <v>110</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J4" t="n">
+        <v>110</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>55</v>
+      </c>
+      <c r="J5" t="n">
+        <v>330</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>220</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>220</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>55</v>
+      </c>
+      <c r="J9" t="n">
+        <v>275</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>220</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>275</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>55</v>
+      </c>
+      <c r="J13" t="n">
+        <v>330</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>太原基地·未随队客场</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>220</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>55</v>
+      </c>
+      <c r="J16" t="n">
+        <v>220</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>脚掌骨疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>55</v>
+      </c>
+      <c r="J17" t="n">
+        <v>220</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>220</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>还有点疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>165</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J20" t="n">
+        <v>220</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>55</v>
+      </c>
+      <c r="J21" t="n">
+        <v>165</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>太原基地·未随队客场</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>太原基地·未随队客场</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MCL恢复期</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J25" t="n">
+        <v>165</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>55</v>
+      </c>
+      <c r="J26" t="n">
+        <v>165</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>左后群轻微紧点</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>165</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J28" t="n">
+        <v>165</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>太原基地·未随队客场</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>训练</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>55</v>
+      </c>
+      <c r="J30" t="n">
+        <v>110</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7/18 MD-1·客场备战大连英博B(明日7/19比赛) | 55min | 22人参训 | 均RPE 3.6 | 总sRPE 4400</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>缺席7人: 布格拉汗(MCL)+太原基地4人(刘/朱/戚/董)+凌中阳/丁云峰未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>赛前: 张海轩脚踝D4 王捷左膝 巫林峰脚掌 谢锦政内踝 艾沙江左后群 | 何麟立腘绳肌已恢复</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -6293,7 +7611,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/11-7/17)</t>
+          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/12-7/18)</t>
         </is>
       </c>
     </row>
@@ -6352,64 +7670,69 @@
           <t>风险</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>7/6</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>7/8</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>7/9</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>7/10</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>7/11</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>7/12</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>7/13</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>7/14</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="P3" s="15" t="inlineStr">
         <is>
           <t>7/15</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t>7/16</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="R3" s="15" t="inlineStr">
         <is>
           <t>7/17</t>
+        </is>
+      </c>
+      <c r="S3" s="15" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6425,10 +7748,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1637</v>
+        <v>1677</v>
       </c>
       <c r="D4" t="n">
-        <v>233.9</v>
+        <v>239.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -6467,6 +7790,9 @@
       <c r="Q4" t="n">
         <v>205</v>
       </c>
+      <c r="S4" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6480,10 +7806,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1499</v>
+        <v>1539</v>
       </c>
       <c r="D5" t="n">
-        <v>214.1</v>
+        <v>219.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -6522,6 +7848,9 @@
       <c r="Q5" t="n">
         <v>205</v>
       </c>
+      <c r="S5" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6535,10 +7864,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1145</v>
+        <v>1185</v>
       </c>
       <c r="D6" t="n">
-        <v>163.6</v>
+        <v>169.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -6577,6 +7906,9 @@
       <c r="Q6" t="n">
         <v>205</v>
       </c>
+      <c r="S6" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6590,10 +7922,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1539</v>
+        <v>1764</v>
       </c>
       <c r="D7" t="n">
-        <v>219.9</v>
+        <v>252</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -6632,6 +7964,9 @@
       <c r="Q7" t="n">
         <v>246</v>
       </c>
+      <c r="S7" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6645,10 +7980,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>1396</v>
       </c>
       <c r="D8" t="n">
-        <v>178</v>
+        <v>199.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -6687,6 +8022,9 @@
       <c r="Q8" t="n">
         <v>246</v>
       </c>
+      <c r="S8" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6746,10 +8084,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1324</v>
+        <v>1474</v>
       </c>
       <c r="D10" t="n">
-        <v>189.1</v>
+        <v>210.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -6788,6 +8126,9 @@
       <c r="Q10" t="n">
         <v>246</v>
       </c>
+      <c r="S10" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6801,10 +8142,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1186</v>
+        <v>1391</v>
       </c>
       <c r="D11" t="n">
-        <v>169.4</v>
+        <v>198.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -6843,6 +8184,9 @@
       <c r="Q11" t="n">
         <v>246</v>
       </c>
+      <c r="S11" t="n">
+        <v>275</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6856,10 +8200,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1302</v>
+        <v>1452</v>
       </c>
       <c r="D12" t="n">
-        <v>186</v>
+        <v>207.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -6898,6 +8242,9 @@
       <c r="Q12" t="n">
         <v>164</v>
       </c>
+      <c r="S12" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6911,10 +8258,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1384</v>
+        <v>1589</v>
       </c>
       <c r="D13" t="n">
-        <v>197.7</v>
+        <v>227</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -6953,6 +8300,9 @@
       <c r="Q13" t="n">
         <v>246</v>
       </c>
+      <c r="S13" t="n">
+        <v>275</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7009,10 +8359,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1384</v>
+        <v>1644</v>
       </c>
       <c r="D15" t="n">
-        <v>197.7</v>
+        <v>234.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -7042,6 +8392,9 @@
       <c r="Q15" t="n">
         <v>246</v>
       </c>
+      <c r="S15" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7083,10 +8436,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1565</v>
+        <v>1750</v>
       </c>
       <c r="D17" t="n">
-        <v>223.6</v>
+        <v>250</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -7125,6 +8478,9 @@
       <c r="Q17" t="n">
         <v>246</v>
       </c>
+      <c r="S17" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7138,10 +8494,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1330</v>
+        <v>1515</v>
       </c>
       <c r="D18" t="n">
-        <v>190</v>
+        <v>216.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -7180,6 +8536,9 @@
       <c r="Q18" t="n">
         <v>287</v>
       </c>
+      <c r="S18" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7193,10 +8552,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1390</v>
+        <v>1575</v>
       </c>
       <c r="D19" t="n">
-        <v>198.6</v>
+        <v>225</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -7235,6 +8594,9 @@
       <c r="Q19" t="n">
         <v>287</v>
       </c>
+      <c r="S19" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7248,10 +8610,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1264</v>
+        <v>1414</v>
       </c>
       <c r="D20" t="n">
-        <v>180.6</v>
+        <v>202</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -7290,6 +8652,9 @@
       <c r="Q20" t="n">
         <v>246</v>
       </c>
+      <c r="S20" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7303,10 +8668,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1223</v>
+        <v>1318</v>
       </c>
       <c r="D21" t="n">
-        <v>174.7</v>
+        <v>188.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -7345,6 +8710,9 @@
       <c r="Q21" t="n">
         <v>205</v>
       </c>
+      <c r="S21" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7358,10 +8726,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1246</v>
+        <v>1396</v>
       </c>
       <c r="D22" t="n">
-        <v>178</v>
+        <v>199.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -7400,6 +8768,9 @@
       <c r="Q22" t="n">
         <v>246</v>
       </c>
+      <c r="S22" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7413,10 +8784,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>888</v>
+        <v>983</v>
       </c>
       <c r="D23" t="n">
-        <v>126.9</v>
+        <v>140.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -7449,6 +8820,9 @@
       <c r="Q23" t="n">
         <v>105</v>
       </c>
+      <c r="S23" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7462,10 +8836,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>760</v>
+        <v>690</v>
       </c>
       <c r="D24" t="n">
-        <v>108.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -7564,10 +8938,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1129</v>
+        <v>1259</v>
       </c>
       <c r="D27" t="n">
-        <v>161.3</v>
+        <v>179.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -7606,6 +8980,9 @@
       <c r="Q27" t="n">
         <v>164</v>
       </c>
+      <c r="S27" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7619,10 +8996,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1538</v>
+        <v>1598</v>
       </c>
       <c r="D28" t="n">
-        <v>219.7</v>
+        <v>228.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -7661,6 +9038,9 @@
       <c r="Q28" t="n">
         <v>287</v>
       </c>
+      <c r="S28" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7674,10 +9054,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1443</v>
+        <v>1538</v>
       </c>
       <c r="D29" t="n">
-        <v>206.1</v>
+        <v>219.7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -7716,6 +9096,9 @@
       <c r="Q29" t="n">
         <v>287</v>
       </c>
+      <c r="S29" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7729,10 +9112,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1345</v>
+        <v>1475</v>
       </c>
       <c r="D30" t="n">
-        <v>192.1</v>
+        <v>210.7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -7771,6 +9154,9 @@
       <c r="Q30" t="n">
         <v>164</v>
       </c>
+      <c r="S30" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7784,10 +9170,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="D31" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -7839,10 +9225,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -7853,6 +9239,9 @@
         <is>
           <t>📊 数据不足</t>
         </is>
+      </c>
+      <c r="S32" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="34">
@@ -7881,7 +9270,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -7903,6 +9292,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -9149,7 +10539,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -9171,6 +10561,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -10369,7 +11760,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -10391,6 +11782,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -11447,7 +12839,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -11469,6 +12861,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -12699,7 +14092,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -12721,6 +14114,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -13886,7 +15280,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -15091,7 +16485,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -16071,7 +17465,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="12" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="14" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1237,7 +1239,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1259,7 +1261,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -2517,7 +2518,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -3796,7 +3797,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -5129,7 +5129,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -5156,7 +5155,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -6261,7 +6260,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -7564,7 +7562,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -7597,8 +7594,2074 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J2" t="n">
+        <v>760</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>95</v>
+      </c>
+      <c r="J5" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>75</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>替补未上场·比赛日疲劳</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>69</v>
+      </c>
+      <c r="J15" t="n">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>69</v>
+      </c>
+      <c r="J16" t="n">
+        <v>483</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>脚掌骨疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n">
+        <v>95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>75</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>替补未上场·比赛日疲劳</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>75</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>替补未上场·比赛日疲劳</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>替补</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>替补未上场·比赛日疲劳</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>85</v>
+      </c>
+      <c r="J25" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" t="n">
+        <v>95</v>
+      </c>
+      <c r="J26" t="n">
+        <v>950</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>左后群稍微紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n">
+        <v>95</v>
+      </c>
+      <c r="J27" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>26</v>
+      </c>
+      <c r="J28" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>比赛</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>26</v>
+      </c>
+      <c r="J30" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>⚽ 7/19 客vs大连英博B 2-1 | 95min | 16人上场 | 总sRPE≈9344 | 4人RPE=10 | 19人晨间问卷</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>缺席</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>行程</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>返回太原</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7/20 行程日·大连→太原 | 无训练 | 晨间待填 | 7/21放假 7/22力量房</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -7611,7 +9674,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/12-7/18)</t>
+          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/14-7/20)</t>
         </is>
       </c>
     </row>
@@ -7735,6 +9798,16 @@
           <t>7/18</t>
         </is>
       </c>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+      <c r="U3" s="15" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7748,10 +9821,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1677</v>
+        <v>2137</v>
       </c>
       <c r="D4" t="n">
-        <v>239.6</v>
+        <v>305.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7793,6 +9866,9 @@
       <c r="S4" t="n">
         <v>110</v>
       </c>
+      <c r="T4" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7806,10 +9882,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1539</v>
+        <v>1349</v>
       </c>
       <c r="D5" t="n">
-        <v>219.9</v>
+        <v>192.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7851,6 +9927,9 @@
       <c r="S5" t="n">
         <v>110</v>
       </c>
+      <c r="T5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7864,10 +9943,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1185</v>
+        <v>1055</v>
       </c>
       <c r="D6" t="n">
-        <v>169.3</v>
+        <v>150.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -7909,6 +9988,9 @@
       <c r="S6" t="n">
         <v>110</v>
       </c>
+      <c r="T6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7922,10 +10004,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1764</v>
+        <v>2474</v>
       </c>
       <c r="D7" t="n">
-        <v>252</v>
+        <v>353.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7967,6 +10049,9 @@
       <c r="S7" t="n">
         <v>330</v>
       </c>
+      <c r="T7" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7980,10 +10065,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1396</v>
+        <v>1881</v>
       </c>
       <c r="D8" t="n">
-        <v>199.4</v>
+        <v>268.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -8025,6 +10110,9 @@
       <c r="S8" t="n">
         <v>220</v>
       </c>
+      <c r="T8" t="n">
+        <v>665</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8084,10 +10172,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1474</v>
+        <v>1296</v>
       </c>
       <c r="D10" t="n">
-        <v>210.6</v>
+        <v>185.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -8129,6 +10217,9 @@
       <c r="S10" t="n">
         <v>220</v>
       </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8142,10 +10233,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1391</v>
+        <v>1971</v>
       </c>
       <c r="D11" t="n">
-        <v>198.7</v>
+        <v>281.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -8187,6 +10278,9 @@
       <c r="S11" t="n">
         <v>275</v>
       </c>
+      <c r="T11" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8200,10 +10294,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1452</v>
+        <v>1213</v>
       </c>
       <c r="D12" t="n">
-        <v>207.4</v>
+        <v>173.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -8245,6 +10339,9 @@
       <c r="S12" t="n">
         <v>220</v>
       </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8258,10 +10355,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1589</v>
+        <v>2204</v>
       </c>
       <c r="D13" t="n">
-        <v>227</v>
+        <v>314.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -8303,6 +10400,9 @@
       <c r="S13" t="n">
         <v>275</v>
       </c>
+      <c r="T13" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8359,10 +10459,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1644</v>
+        <v>1479</v>
       </c>
       <c r="D15" t="n">
-        <v>234.9</v>
+        <v>211.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -8395,6 +10495,9 @@
       <c r="S15" t="n">
         <v>330</v>
       </c>
+      <c r="T15" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8436,10 +10539,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1750</v>
+        <v>1933</v>
       </c>
       <c r="D17" t="n">
-        <v>250</v>
+        <v>276.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -8481,6 +10584,9 @@
       <c r="S17" t="n">
         <v>220</v>
       </c>
+      <c r="T17" t="n">
+        <v>483</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8494,10 +10600,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1515</v>
+        <v>1818</v>
       </c>
       <c r="D18" t="n">
-        <v>216.4</v>
+        <v>259.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -8539,6 +10645,9 @@
       <c r="S18" t="n">
         <v>220</v>
       </c>
+      <c r="T18" t="n">
+        <v>483</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8552,10 +10661,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1575</v>
+        <v>2285</v>
       </c>
       <c r="D19" t="n">
-        <v>225</v>
+        <v>326.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -8597,6 +10706,9 @@
       <c r="S19" t="n">
         <v>220</v>
       </c>
+      <c r="T19" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8610,10 +10722,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1414</v>
+        <v>1369</v>
       </c>
       <c r="D20" t="n">
-        <v>202</v>
+        <v>195.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -8655,6 +10767,9 @@
       <c r="S20" t="n">
         <v>220</v>
       </c>
+      <c r="T20" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8668,10 +10783,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1318</v>
+        <v>1228</v>
       </c>
       <c r="D21" t="n">
-        <v>188.3</v>
+        <v>175.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -8713,6 +10828,9 @@
       <c r="S21" t="n">
         <v>165</v>
       </c>
+      <c r="T21" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8726,10 +10844,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1396</v>
+        <v>1351</v>
       </c>
       <c r="D22" t="n">
-        <v>199.4</v>
+        <v>193</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -8771,6 +10889,9 @@
       <c r="S22" t="n">
         <v>220</v>
       </c>
+      <c r="T22" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8784,10 +10905,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>983</v>
+        <v>888</v>
       </c>
       <c r="D23" t="n">
-        <v>140.4</v>
+        <v>126.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -8823,6 +10944,9 @@
       <c r="S23" t="n">
         <v>165</v>
       </c>
+      <c r="T23" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8836,10 +10960,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>690</v>
+        <v>450</v>
       </c>
       <c r="D24" t="n">
-        <v>98.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -8938,10 +11062,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1259</v>
+        <v>1844</v>
       </c>
       <c r="D27" t="n">
-        <v>179.9</v>
+        <v>263.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -8983,6 +11107,9 @@
       <c r="S27" t="n">
         <v>165</v>
       </c>
+      <c r="T27" t="n">
+        <v>765</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8996,10 +11123,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1598</v>
+        <v>2368</v>
       </c>
       <c r="D28" t="n">
-        <v>228.3</v>
+        <v>338.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -9041,6 +11168,9 @@
       <c r="S28" t="n">
         <v>165</v>
       </c>
+      <c r="T28" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9054,10 +11184,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1538</v>
+        <v>2308</v>
       </c>
       <c r="D29" t="n">
-        <v>219.7</v>
+        <v>329.7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -9099,6 +11229,9 @@
       <c r="S29" t="n">
         <v>165</v>
       </c>
+      <c r="T29" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9112,10 +11245,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1475</v>
+        <v>1563</v>
       </c>
       <c r="D30" t="n">
-        <v>210.7</v>
+        <v>223.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -9157,6 +11290,9 @@
       <c r="S30" t="n">
         <v>165</v>
       </c>
+      <c r="T30" t="n">
+        <v>208</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9170,10 +11306,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="D31" t="n">
-        <v>84</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -9225,10 +11361,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>110</v>
+        <v>292</v>
       </c>
       <c r="D32" t="n">
-        <v>15.7</v>
+        <v>41.7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -9242,6 +11378,9 @@
       </c>
       <c r="S32" t="n">
         <v>110</v>
+      </c>
+      <c r="T32" t="n">
+        <v>182</v>
       </c>
     </row>
     <row r="34">
@@ -9270,7 +11409,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -9292,7 +11431,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -10539,7 +12677,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -10561,7 +12699,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -11760,7 +13897,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -11782,7 +13919,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -12839,7 +14975,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -12861,7 +14997,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -14092,7 +16227,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -14114,7 +16249,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -15280,7 +17414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -16485,7 +18619,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -17465,7 +19599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="14" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="18" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30,8 +33,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="32">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+  </numFmts>
+  <fonts count="37">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -256,8 +261,32 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -462,8 +491,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00992828"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -643,6 +677,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -791,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -826,6 +874,26 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2761,7 +2829,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>脚踝有一点不舒服 ⚠️</t>
+          <t>脚踝有一点不舒服</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2919,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -2941,7 +3009,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>酸痛未填</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -2986,7 +3054,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>左膝盖 ⚠️</t>
+          <t>左膝盖</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3144,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -3191,6 +3259,15 @@
           <t>缺席</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>375</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>MCL恢复期</t>
@@ -3238,7 +3315,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>脚掌骨疼 ⚠️</t>
+          <t>脚掌骨疼</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3540,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>仅热身+抢圈+转换→未参加比赛</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3585,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>发烧 🔴 仅热身+抢圈→退出</t>
+          <t>有些发烧</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3810,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>仅热身+抢圈+转换→未参加比赛</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -3753,6 +3830,15 @@
           <t>后卫</t>
         </is>
       </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>轻量训练</t>
@@ -3783,6 +3869,12 @@
           <t>后卫</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>轻量训练</t>
@@ -3793,7 +3885,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>试训·仅热身+抢圈+转换→未参加比赛</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -3928,7 +4020,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>脚踝痛 🆕</t>
+          <t>脚踝痛</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4245,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4380,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>左膝 ⚠️</t>
+          <t>左膝</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4470,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>跟队训练·仍停赛(7/19vs大连英博B)</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4605,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>脚掌骨疼 ⚠️</t>
+          <t>脚掌不适</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4830,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>仅热身+传球+冲刺+长传→未参加战术演练</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4875,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>肚子不舒服·仅参加动态拉伸</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5100,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>仅热身+传球+冲刺+长传→未参加战术演练</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -5033,6 +5125,15 @@
           <t>缺席</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>375</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>MCL恢复期</t>
@@ -5055,6 +5156,15 @@
           <t>后卫</t>
         </is>
       </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>轻量训练</t>
@@ -5085,6 +5195,12 @@
           <t>后卫</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>轻量训练</t>
@@ -5095,7 +5211,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>试训·仅热身+传球+冲刺+长传→未参加战术演练</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5373,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>脚踝痛·第2天 ⚠️</t>
+          <t>脚踝痛</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5661,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>左膝持续 ⚠️</t>
+          <t>左膝</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5790,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -5725,7 +5841,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>腘绳肌微紧 🆕</t>
+          <t>腘绳肌微紧</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5877,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>脚掌不适持续+睡眠4 ⚠️</t>
+          <t>脚掌不适</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5949,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>内踝不适 🆕</t>
+          <t>内踝不适</t>
         </is>
       </c>
     </row>
@@ -5905,7 +6021,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>睡眠4·偏差</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -5926,7 +6042,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -5998,7 +6114,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -6013,7 +6129,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6228,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>左大腿后群有点紧 🆕</t>
+          <t>左大腿后群有点紧</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6300,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>睡眠4·偏差</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6372,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>已签约·正式入队🆕</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6507,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>脚踝痛·第4天</t>
+          <t>脚踝痛</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6717,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>未跟队</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7356,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>太原基地·未随队客场</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -7263,6 +7379,9 @@
       <c r="D23" t="n">
         <v>2</v>
       </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>缺席</t>
@@ -7270,7 +7389,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>太原基地·未随队客场</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7632,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>太原基地·未随队客场</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -7833,6 +7952,11 @@
       <c r="J5" t="n">
         <v>950</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7873,6 +7997,11 @@
       <c r="J6" t="n">
         <v>665</v>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7940,6 +8069,11 @@
       <c r="J8" t="n">
         <v>2</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7980,6 +8114,11 @@
       <c r="J9" t="n">
         <v>760</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8065,6 +8204,11 @@
       <c r="J11" t="n">
         <v>855</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8134,7 +8278,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>替补未上场·比赛日疲劳</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -8204,6 +8348,11 @@
       <c r="J15" t="n">
         <v>483</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8289,6 +8438,11 @@
       <c r="J17" t="n">
         <v>950</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8371,6 +8525,11 @@
       <c r="J19" t="n">
         <v>30</v>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8413,7 +8572,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>替补未上场·比赛日疲劳</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8617,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>替补未上场·比赛日疲劳</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -8478,6 +8637,9 @@
           <t>中场</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>缺席</t>
@@ -8505,6 +8667,9 @@
           <t>中场</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>缺席</t>
@@ -8512,7 +8677,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>未随队</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -8582,6 +8747,11 @@
       <c r="J25" t="n">
         <v>765</v>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8667,6 +8837,11 @@
       <c r="J27" t="n">
         <v>950</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8707,6 +8882,11 @@
       <c r="J28" t="n">
         <v>208</v>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8774,8 +8954,12 @@
       <c r="J30" t="n">
         <v>182</v>
       </c>
-    </row>
-    <row r="31"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -9645,7 +9829,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7/20 行程日·大连→太原 | 无训练 | 晨间待填 | 7/21放假 7/22力量房</t>
+          <t>7/20 休息日·在大连 | 7/21返程太原</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9844,984 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U35"/>
+  <dimension ref="A1:L30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>肌肉酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>肌肉酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>康复训练</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>跑步机直线15✅ | 无变向</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>★今日归队·MCL恢复期(第5周)·直线15km/h✅·变速/变向/急停/启动受限·目标两周内跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>肌肉酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>肌肉酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9669,12 +10830,13 @@
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/14-7/20)</t>
+          <t>📊 ACWR 急慢性负荷比 · 滚动7天 (7/17-7/23)</t>
         </is>
       </c>
     </row>
@@ -9808,6 +10970,16 @@
           <t>7/20</t>
         </is>
       </c>
+      <c r="V3" s="21" t="inlineStr">
+        <is>
+          <t>7/22</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7/23</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9820,11 +10992,11 @@
           <t>门将</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>2137</v>
-      </c>
-      <c r="D4" t="n">
-        <v>305.3</v>
+      <c r="C4" s="23" t="n">
+        <v>2205</v>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>315</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -9869,6 +11041,12 @@
       <c r="T4" t="n">
         <v>760</v>
       </c>
+      <c r="V4" s="22" t="n">
+        <v>780</v>
+      </c>
+      <c r="W4" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9881,11 +11059,11 @@
           <t>门将</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1349</v>
-      </c>
-      <c r="D5" t="n">
-        <v>192.7</v>
+      <c r="C5" s="23" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>188</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -9930,6 +11108,12 @@
       <c r="T5" t="n">
         <v>50</v>
       </c>
+      <c r="V5" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W5" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9942,11 +11126,11 @@
           <t>门将</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D6" t="n">
-        <v>150.7</v>
+      <c r="C6" s="23" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>181</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -9991,6 +11175,12 @@
       <c r="T6" t="n">
         <v>50</v>
       </c>
+      <c r="V6" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W6" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10003,11 +11193,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>2474</v>
-      </c>
-      <c r="D7" t="n">
-        <v>353.4</v>
+      <c r="C7" s="23" t="n">
+        <v>2706</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>387</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -10052,6 +11242,12 @@
       <c r="T7" t="n">
         <v>950</v>
       </c>
+      <c r="V7" s="22" t="n">
+        <v>780</v>
+      </c>
+      <c r="W7" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10064,11 +11260,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1881</v>
-      </c>
-      <c r="D8" t="n">
-        <v>268.7</v>
+      <c r="C8" s="23" t="n">
+        <v>2031</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>290</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10113,6 +11309,12 @@
       <c r="T8" t="n">
         <v>665</v>
       </c>
+      <c r="V8" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W8" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10125,11 +11327,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1074</v>
-      </c>
-      <c r="D9" t="n">
-        <v>153.4</v>
+      <c r="C9" s="23" t="n">
+        <v>1246</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>178</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10159,6 +11361,12 @@
       <c r="Q9" t="n">
         <v>246</v>
       </c>
+      <c r="V9" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W9" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10171,11 +11379,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1296</v>
-      </c>
-      <c r="D10" t="n">
-        <v>185.1</v>
+      <c r="C10" s="23" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>184</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -10220,6 +11428,12 @@
       <c r="T10" t="n">
         <v>2</v>
       </c>
+      <c r="V10" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W10" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10232,11 +11446,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1971</v>
-      </c>
-      <c r="D11" t="n">
-        <v>281.6</v>
+      <c r="C11" s="23" t="n">
+        <v>2281</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>326</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -10281,6 +11495,12 @@
       <c r="T11" t="n">
         <v>760</v>
       </c>
+      <c r="V11" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W11" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10293,11 +11513,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1213</v>
-      </c>
-      <c r="D12" t="n">
-        <v>173.3</v>
+      <c r="C12" s="23" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>198</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -10342,6 +11562,12 @@
       <c r="T12" t="n">
         <v>1</v>
       </c>
+      <c r="V12" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W12" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10354,11 +11580,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>2204</v>
-      </c>
-      <c r="D13" t="n">
-        <v>314.9</v>
+      <c r="C13" s="23" t="n">
+        <v>2376</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>339</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -10403,6 +11629,12 @@
       <c r="T13" t="n">
         <v>855</v>
       </c>
+      <c r="V13" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W13" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10415,11 +11647,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>817</v>
-      </c>
-      <c r="D14" t="n">
-        <v>116.7</v>
+      <c r="C14" s="23" t="n">
+        <v>1075</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>154</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -10446,6 +11678,12 @@
       <c r="Q14" t="n">
         <v>205</v>
       </c>
+      <c r="V14" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W14" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10458,11 +11696,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1479</v>
-      </c>
-      <c r="D15" t="n">
-        <v>211.3</v>
+      <c r="C15" s="23" t="n">
+        <v>1601</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>229</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -10498,6 +11736,12 @@
       <c r="T15" t="n">
         <v>75</v>
       </c>
+      <c r="V15" s="22" t="n">
+        <v>650</v>
+      </c>
+      <c r="W15" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10510,11 +11754,11 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
+      <c r="C16" s="23" t="n">
+        <v>770</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>110</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -10525,6 +11769,12 @@
         <is>
           <t>📊 数据不足</t>
         </is>
+      </c>
+      <c r="V16" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W16" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="17">
@@ -10538,11 +11788,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1933</v>
-      </c>
-      <c r="D17" t="n">
-        <v>276.1</v>
+      <c r="C17" s="23" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>253</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -10587,6 +11837,12 @@
       <c r="T17" t="n">
         <v>483</v>
       </c>
+      <c r="V17" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W17" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10599,11 +11855,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1818</v>
-      </c>
-      <c r="D18" t="n">
-        <v>259.7</v>
+      <c r="C18" s="23" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>259</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -10648,6 +11904,12 @@
       <c r="T18" t="n">
         <v>483</v>
       </c>
+      <c r="V18" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W18" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10660,11 +11922,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>2285</v>
-      </c>
-      <c r="D19" t="n">
-        <v>326.4</v>
+      <c r="C19" s="23" t="n">
+        <v>2327</v>
+      </c>
+      <c r="D19" s="23" t="n">
+        <v>332</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -10709,6 +11971,12 @@
       <c r="T19" t="n">
         <v>950</v>
       </c>
+      <c r="V19" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W19" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10721,11 +11989,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1369</v>
-      </c>
-      <c r="D20" t="n">
-        <v>195.6</v>
+      <c r="C20" s="23" t="n">
+        <v>1411</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>202</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -10770,6 +12038,12 @@
       <c r="T20" t="n">
         <v>75</v>
       </c>
+      <c r="V20" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W20" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10782,11 +12056,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1228</v>
-      </c>
-      <c r="D21" t="n">
-        <v>175.4</v>
+      <c r="C21" s="23" t="n">
+        <v>1220</v>
+      </c>
+      <c r="D21" s="23" t="n">
+        <v>174</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -10831,6 +12105,12 @@
       <c r="T21" t="n">
         <v>30</v>
       </c>
+      <c r="V21" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W21" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10843,11 +12123,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1351</v>
-      </c>
-      <c r="D22" t="n">
-        <v>193</v>
+      <c r="C22" s="23" t="n">
+        <v>1311</v>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>187</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -10892,6 +12172,12 @@
       <c r="T22" t="n">
         <v>75</v>
       </c>
+      <c r="V22" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W22" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10904,11 +12190,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>888</v>
-      </c>
-      <c r="D23" t="n">
-        <v>126.9</v>
+      <c r="C23" s="23" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>152</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -10947,6 +12233,12 @@
       <c r="T23" t="n">
         <v>25</v>
       </c>
+      <c r="V23" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W23" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10959,11 +12251,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>450</v>
-      </c>
-      <c r="D24" t="n">
-        <v>64.3</v>
+      <c r="C24" s="23" t="n">
+        <v>735</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>105</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -10993,6 +12285,12 @@
       <c r="Q24" t="n">
         <v>15</v>
       </c>
+      <c r="V24" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W24" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11005,11 +12303,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
+      <c r="C25" s="23" t="n">
+        <v>880</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>126</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -11020,6 +12318,12 @@
         <is>
           <t>📊 数据不足</t>
         </is>
+      </c>
+      <c r="V25" s="22" t="n">
+        <v>780</v>
+      </c>
+      <c r="W25" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -11033,11 +12337,11 @@
           <t>中场</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
+      <c r="C26" s="23" t="n">
+        <v>490</v>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>70</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -11048,6 +12352,12 @@
         <is>
           <t>📊 数据不足</t>
         </is>
+      </c>
+      <c r="V26" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="W26" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="27">
@@ -11061,11 +12371,11 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1844</v>
-      </c>
-      <c r="D27" t="n">
-        <v>263.4</v>
+      <c r="C27" s="23" t="n">
+        <v>1864</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>266</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -11110,6 +12420,12 @@
       <c r="T27" t="n">
         <v>765</v>
       </c>
+      <c r="V27" s="22" t="n">
+        <v>520</v>
+      </c>
+      <c r="W27" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11122,11 +12438,11 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D28" t="n">
-        <v>338.3</v>
+      <c r="C28" s="23" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>286</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -11171,6 +12487,12 @@
       <c r="T28" t="n">
         <v>950</v>
       </c>
+      <c r="V28" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="W28" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11183,11 +12505,11 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>2308</v>
-      </c>
-      <c r="D29" t="n">
-        <v>329.7</v>
+      <c r="C29" s="23" t="n">
+        <v>2062</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>295</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -11232,6 +12554,12 @@
       <c r="T29" t="n">
         <v>950</v>
       </c>
+      <c r="V29" s="22" t="n">
+        <v>360</v>
+      </c>
+      <c r="W29" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11244,11 +12572,11 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1563</v>
-      </c>
-      <c r="D30" t="n">
-        <v>223.3</v>
+      <c r="C30" s="23" t="n">
+        <v>1077</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>154</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -11293,6 +12621,12 @@
       <c r="T30" t="n">
         <v>208</v>
       </c>
+      <c r="V30" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="W30" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11305,11 +12639,11 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>528</v>
-      </c>
-      <c r="D31" t="n">
-        <v>75.40000000000001</v>
+      <c r="C31" s="23" t="n">
+        <v>63</v>
+      </c>
+      <c r="D31" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -11348,6 +12682,9 @@
       <c r="Q31" t="n">
         <v>63</v>
       </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11360,11 +12697,11 @@
           <t>前锋</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>292</v>
-      </c>
-      <c r="D32" t="n">
-        <v>41.7</v>
+      <c r="C32" s="23" t="n">
+        <v>832</v>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>119</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -11382,22 +12719,3479 @@
       <c r="T32" t="n">
         <v>182</v>
       </c>
+      <c r="V32" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="W32" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>📊 数据不足</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>250</v>
+      </c>
+      <c r="H33" t="n">
+        <v>36</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>⚠️ 滚动7天窗口(7/11-7/17)。ACWR需28天慢性负荷才有意义，当前仅12天基线，仅展示每日sRPE与7天急性总量。8月初达28天后启用标准ACWR。</t>
-        </is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>180</v>
+      </c>
+      <c r="D34" t="n">
+        <v>26</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>📊 数据不足</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>280</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>180</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7/17行程日全员sRPE=0 · 7/19比赛日后急性负荷将上升 · 三名新签(刘子洁/董德/努尔扎提)自7/17起计入</t>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>📊 数据不足</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>滚动7天窗口(7/17-7/23) · 7/21=放假(sRPE=0) · 7/23=MD-3三球门对抗 · 7/26主场vs海门</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G1" s="17" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" s="17" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="I1" s="17" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" s="17" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="K2" s="18" t="inlineStr">
+        <is>
+          <t>脚踝痛·冰敷</t>
+        </is>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t>上午力量房OK | 场地RPE=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K3" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L3" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L4" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>新人·轻量 | 场地RPE=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>累</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>降量50% | 场地RPE=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>休足 | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L10" s="18" t="inlineStr">
+        <is>
+          <t>降量50% | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>左膝·冰敷</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>康复组 | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K12" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>降量50% | 场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K14" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>睡眠差⚠️</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>睡5·注意 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>布格拉汗</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>力量房</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K17" s="18" t="inlineStr">
+        <is>
+          <t>MCL·冰敷</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>归队D2·AM力量房全跟(上肢正常·下肢自重)+PM场地单独·RPE=3·进展顺利</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
+        <is>
+          <t>脚掌·冰敷</t>
+        </is>
+      </c>
+      <c r="L18" s="18" t="inlineStr">
+        <is>
+          <t>康复组·坐姿优先 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>脚腕疼🆕</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>降量50%·新信号 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L20" s="18" t="inlineStr">
+        <is>
+          <t>内踝已恢复·正常组 | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L21" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L22" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L23" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L24" s="18" t="inlineStr">
+        <is>
+          <t>场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L25" s="18" t="inlineStr">
+        <is>
+          <t>新人·投入 | 场地RPE=6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>新人·轻量 | 场地RPE=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>力量房</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L27" s="18" t="inlineStr">
+        <is>
+          <t>新人·缺填</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>力量房+场地</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J28" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K28" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L28" s="18" t="inlineStr">
+        <is>
+          <t>降量50% | 场地RPE=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>艾沙江</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>力量房</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J29" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="K29" s="18" t="inlineStr">
+        <is>
+          <t>后群观察</t>
+        </is>
+      </c>
+      <c r="L29" s="18" t="inlineStr">
+        <is>
+          <t>臀桥代深蹲·不硬拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>帕尔曼江</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>力量房</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="inlineStr">
+        <is>
+          <t>降量50%·睡4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>阿西江</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>力量房</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K31" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L31" s="18" t="inlineStr">
+        <is>
+          <t>降量50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>努尔扎提</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>7/22 上午力量房(60min·均RPE~4.5)+下午场地训练(均RPE~4.5) | 31人参训 | 布格拉汗归队D2✅ | 🆕张辉脚腕疼 | ⚠️何麟立睡5 | 一日双训·维持日</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="K32" s="18" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L32" s="18" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>7/22 AM力量房60min(均RPE~4.5)+PM场地70min(均RPE~4.5) | 31人参训 | 一日双训·MD-4维持 | 场地:动态拉伸→抢圈→传接球→射门2线路→13v13+4GK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A34:L34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>训练/比赛</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RPE</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>时长</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>恢复干预</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>脚踝痛·冰敷</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>脚踝D10·RPE偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" t="n">
+        <v>300</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>肩膀疼</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" t="n">
+        <v>250</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J5" t="n">
+        <v>250</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>新人·睡眠缺填</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>400</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>⚠️⚠️⚠️ 降量·软组织放松</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7/19跑10km⚡+7/22全量力量→RPE=8全队最高·累积疲劳·D-3必须降量</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" t="n">
+        <v>250</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>350</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>停赛休足·三球门覆盖面积大→RPE偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="n">
+        <v>300</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>350</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>⚠️ 关注</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>连续两天RPE偏高·睡3疲3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J11" t="n">
+        <v>350</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>左膝·酸=4⚠️</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>髌腱炎管理·酸痛突增·需评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" t="n">
+        <v>350</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>正常酸痛</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>RPE偏高·三球门覆盖大</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J13" t="n">
+        <v>350</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>正常酸痛</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>RPE偏高</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>场地50min+4v4(10min)</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>300</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4v4前10min→后换回主组</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4v4体能·50min</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>250</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4v4组·体能教练带·投入正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>300</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>睡质5→2·恢复良好✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4v4体能·50min</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>250</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>MCL·监控变向</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>MCL D+2·4v4参与·变向可控✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" t="n">
+        <v>300</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>脚掌·正常</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>正常训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J19" t="n">
+        <v>350</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>⚠️ 肌肉酸</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>7/19跑10km⚡+脚腕疼史→今日肌肉酸·需监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" t="n">
+        <v>350</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>内踝已恢复·疲劳缺填</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>50</v>
+      </c>
+      <c r="J21" t="n">
+        <v>300</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>50</v>
+      </c>
+      <c r="J22" t="n">
+        <v>250</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4v4体能·50min</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" t="n">
+        <v>250</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>酸痛=4</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>4v4组·酸痛偏高·正常训练反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4v4体能·50min</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>50</v>
+      </c>
+      <c r="J24" t="n">
+        <v>200</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>4v4组·正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4v4体能·50min</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J25" t="n">
+        <v>100</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>⚠️ 睡4+RPE=2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>4v4组·投入度待观察·睡眠恶化</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>4v4体能·50min</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>50</v>
+      </c>
+      <c r="J26" t="n">
+        <v>100</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>4v4组·10min替换杨文杰·新人适应</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>薛悦伟</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>未填</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>50</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>新人·全部缺填</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J28" t="n">
+        <v>250</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>恢复良好·RPE回落✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>50</v>
+      </c>
+      <c r="J29" t="n">
+        <v>300</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>后群·监控</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>后群观察中·正常训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>50</v>
+      </c>
+      <c r="J30" t="n">
+        <v>300</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>睡眠4→3改善·RPE稳定</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>50</v>
+      </c>
+      <c r="J31" t="n">
+        <v>300</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>戚博(U21)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>未填</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>50</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>未填数据·待补</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>场地50min</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J33" t="n">
+        <v>300</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7/23 MD-3 · 场地50min · 头球游戏+11v11三球门×2+20min正式·同步4v4 · 32人参训 · 均RPE≈5.7 · ⚠️张俊哲RPE=8 · 备战7/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:L35"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20084,7 +24878,7 @@
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>左膝盖稍微痛痛 | 左膝仍不适⚠️</t>
+          <t>左膝盖稍微痛痛</t>
         </is>
       </c>
     </row>
@@ -20242,9 +25036,15 @@
           <t>后卫</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>训练</t>
@@ -20258,7 +25058,7 @@
       <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>试训球员</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -20332,9 +25132,15 @@
           <t>缺席</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>375</v>
+      </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
     </row>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -1307,7 +1307,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -2586,7 +2586,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5271,7 +5271,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10822,7 +10822,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>📊 数据不足</t>
+          <t>🚫租借</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -16124,15 +16124,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>未填</t>
+          <t>租借离队</t>
         </is>
       </c>
       <c r="I32" t="n">
         <v>50</v>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>→海门珂缔缘</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>未填数据·待补</t>
+          <t>数据停止采集</t>
         </is>
       </c>
     </row>
@@ -16203,7 +16208,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -17471,7 +17476,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -18691,7 +18696,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -19769,7 +19774,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -21021,7 +21026,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -22208,7 +22213,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -23413,7 +23418,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -24393,7 +24398,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -1373,6 +1373,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1448,7 +1449,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1484,7 +1485,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1511,7 +1512,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1547,7 +1548,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1583,7 +1584,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1610,7 +1611,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1646,7 +1647,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1682,7 +1683,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1718,7 +1719,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1745,7 +1746,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1786,7 +1787,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1827,7 +1828,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1863,7 +1864,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1899,7 +1900,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1940,7 +1941,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1981,7 +1982,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2017,7 +2018,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2053,7 +2054,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2094,7 +2095,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2135,7 +2136,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2162,7 +2163,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2198,7 +2199,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2239,7 +2240,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2280,7 +2281,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2321,7 +2322,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2357,7 +2358,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2393,7 +2394,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2434,7 +2435,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2470,7 +2471,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2590,7 +2591,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -2635,7 +2636,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2680,7 +2681,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2725,7 +2726,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2770,7 +2771,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2815,7 +2816,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2860,7 +2861,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2905,7 +2906,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2950,7 +2951,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2995,7 +2996,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3040,7 +3041,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -3085,7 +3086,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -3130,7 +3131,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3175,7 +3176,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3211,7 +3212,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3256,7 +3257,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3301,7 +3302,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3346,7 +3347,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3391,7 +3392,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3436,7 +3437,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3481,7 +3482,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3526,7 +3527,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -3571,7 +3572,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3616,7 +3617,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3661,7 +3662,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3706,7 +3707,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3751,7 +3752,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3790,7 +3791,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3813,6 +3814,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -3916,7 +3918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3961,7 +3963,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -4006,7 +4008,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -4051,7 +4053,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -4096,7 +4098,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4141,7 +4143,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4186,7 +4188,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4231,7 +4233,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4276,7 +4278,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4321,7 +4323,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4366,7 +4368,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4411,7 +4413,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -4456,7 +4458,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -4501,7 +4503,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4546,7 +4548,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -4591,7 +4593,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4636,7 +4638,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -4681,7 +4683,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -4726,7 +4728,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4771,7 +4773,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4816,7 +4818,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4861,7 +4863,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4906,7 +4908,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4951,7 +4953,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4996,7 +4998,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5041,7 +5043,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5077,7 +5079,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5116,7 +5118,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -5152,7 +5154,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5169,6 +5171,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -5278,7 +5281,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -5314,7 +5317,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5350,7 +5353,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -5386,7 +5389,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -5422,7 +5425,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -5458,7 +5461,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -5494,7 +5497,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -5530,7 +5533,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5566,7 +5569,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5602,7 +5605,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5638,7 +5641,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5674,7 +5677,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -5710,7 +5713,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -5746,7 +5749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -5782,7 +5785,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -5818,7 +5821,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -5854,7 +5857,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5890,7 +5893,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -5926,7 +5929,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -5962,7 +5965,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -5998,7 +6001,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -6034,7 +6037,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -6070,7 +6073,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6097,7 +6100,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -6133,7 +6136,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -6169,7 +6172,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -6205,7 +6208,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -6241,7 +6244,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -6277,7 +6280,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -6300,6 +6303,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -6403,7 +6407,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -6448,7 +6452,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -6493,7 +6497,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -6538,7 +6542,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -6583,7 +6587,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -6628,7 +6632,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -6658,7 +6662,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -6703,7 +6707,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -6748,7 +6752,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -6793,7 +6797,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -6838,7 +6842,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6865,7 +6869,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -6910,7 +6914,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -6946,7 +6950,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -6991,7 +6995,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -7036,7 +7040,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -7081,7 +7085,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -7126,7 +7130,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -7171,7 +7175,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -7216,7 +7220,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -7261,7 +7265,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -7297,7 +7301,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -7330,7 +7334,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7357,7 +7361,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -7402,7 +7406,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -7447,7 +7451,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -7492,7 +7496,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -7537,7 +7541,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -7573,7 +7577,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -7605,6 +7609,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -7715,7 +7720,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -7760,7 +7765,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -7805,7 +7810,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -7850,7 +7855,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -7895,7 +7900,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -7940,7 +7945,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7967,7 +7972,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8012,7 +8017,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8057,7 +8062,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8102,7 +8107,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -8147,7 +8152,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8174,7 +8179,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -8219,7 +8224,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8246,7 +8251,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -8291,7 +8296,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -8336,7 +8341,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -8381,7 +8386,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -8423,7 +8428,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -8468,7 +8473,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -8513,7 +8518,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -8558,7 +8563,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -8588,7 +8593,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -8618,7 +8623,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8645,7 +8650,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -8690,7 +8695,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -8735,7 +8740,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -8780,7 +8785,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -8825,7 +8830,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8852,7 +8857,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -8884,6 +8889,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -8980,7 +8986,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -9007,7 +9013,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -9034,7 +9040,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -9061,7 +9067,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -9088,7 +9094,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -9115,7 +9121,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -9142,7 +9148,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -9169,7 +9175,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -9196,7 +9202,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9223,7 +9229,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -9250,7 +9256,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9277,7 +9283,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9304,7 +9310,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9331,7 +9337,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -9358,7 +9364,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9385,7 +9391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -9412,7 +9418,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -9439,7 +9445,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9466,7 +9472,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9493,7 +9499,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9520,7 +9526,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9547,7 +9553,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9574,7 +9580,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9601,7 +9607,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9628,7 +9634,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9655,7 +9661,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9682,7 +9688,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9709,7 +9715,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9736,7 +9742,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9750,6 +9756,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -9846,7 +9853,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -9877,7 +9884,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -9908,7 +9915,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9939,7 +9946,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -9970,7 +9977,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10001,7 +10008,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -10032,7 +10039,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -10063,7 +10070,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10094,7 +10101,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10125,7 +10132,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10156,7 +10163,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10187,7 +10194,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -10218,7 +10225,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10249,7 +10256,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10280,7 +10287,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10311,7 +10318,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10342,7 +10349,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -10370,7 +10377,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10401,7 +10408,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10432,7 +10439,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10463,7 +10470,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10494,7 +10501,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10525,7 +10532,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10575,7 +10582,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10606,7 +10613,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -10637,7 +10644,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -10668,7 +10675,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -10699,7 +10706,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10723,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -10828,7 +10835,7 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
@@ -10878,7 +10885,7 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" s="16" t="n">
@@ -10928,7 +10935,7 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
@@ -10978,7 +10985,7 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" s="16" t="n">
@@ -11028,7 +11035,7 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
@@ -11078,7 +11085,7 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" s="16" t="n">
@@ -11128,7 +11135,7 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
@@ -11178,7 +11185,7 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" s="16" t="n">
@@ -11228,7 +11235,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
@@ -11278,7 +11285,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" s="16" t="n">
@@ -11328,7 +11335,7 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
@@ -11378,7 +11385,7 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" s="16" t="n">
@@ -11428,7 +11435,7 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
@@ -11478,7 +11485,7 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" s="16" t="n">
@@ -11528,7 +11535,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
@@ -11578,7 +11585,7 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" s="16" t="n">
@@ -11632,7 +11639,7 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" s="16" t="n">
@@ -11686,7 +11693,7 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
@@ -11736,7 +11743,7 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" s="16" t="n">
@@ -11786,7 +11793,7 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" s="16" t="n">
@@ -11836,7 +11843,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
@@ -11886,7 +11893,7 @@
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
@@ -11936,7 +11943,7 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
@@ -11986,7 +11993,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
@@ -12040,7 +12047,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
@@ -12090,7 +12097,7 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
@@ -12150,7 +12157,7 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
@@ -12200,7 +12207,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
@@ -12250,7 +12257,7 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
@@ -12300,7 +12307,7 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
@@ -12350,7 +12357,7 @@
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
@@ -12383,6 +12390,7 @@
       </c>
       <c r="L32" s="15" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -12482,7 +12490,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -12532,7 +12540,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -12582,7 +12590,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -12627,7 +12635,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -12669,7 +12677,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -12719,7 +12727,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -12764,7 +12772,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -12809,7 +12817,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -12854,7 +12862,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -12904,7 +12912,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -12954,7 +12962,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -13004,7 +13012,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -13054,7 +13062,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -13099,7 +13107,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -13144,7 +13152,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -13189,7 +13197,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -13239,7 +13247,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -13289,7 +13297,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -13339,7 +13347,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -13381,7 +13389,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -13426,7 +13434,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -13471,7 +13479,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -13521,7 +13529,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -13566,7 +13574,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -13616,7 +13624,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -13661,7 +13669,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13691,7 +13699,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -13736,7 +13744,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -13786,7 +13794,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -13831,7 +13839,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -13876,7 +13884,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13911,7 +13919,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -13943,6 +13951,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -15213,6 +15222,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -15247,6 +15257,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -15322,7 +15333,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -15367,7 +15378,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -15412,7 +15423,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -15457,7 +15468,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -15502,7 +15513,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -15547,7 +15558,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -15592,7 +15603,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -15637,7 +15648,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -15682,7 +15693,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -15727,7 +15738,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -15772,7 +15783,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -15817,7 +15828,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -15862,7 +15873,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -15901,7 +15912,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -15946,7 +15957,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -15991,7 +16002,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -16036,7 +16047,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -16081,7 +16092,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -16126,7 +16137,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -16168,7 +16179,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -16210,7 +16221,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -16255,7 +16266,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -16300,7 +16311,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -16345,7 +16356,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -16390,7 +16401,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -16435,7 +16446,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -16545,7 +16556,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" s="11" t="n">
@@ -16595,7 +16606,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" s="13" t="n">
@@ -16641,7 +16652,7 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" s="11" t="n">
@@ -16683,7 +16694,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
@@ -16725,7 +16736,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" s="11" t="n">
@@ -16771,7 +16782,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" s="13" t="n">
@@ -16813,7 +16824,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" s="11" t="n">
@@ -16855,7 +16866,7 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" s="13" t="n">
@@ -16897,7 +16908,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" s="11" t="n">
@@ -16943,7 +16954,7 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" s="13" t="n">
@@ -16993,7 +17004,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
@@ -17035,7 +17046,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" s="13" t="n">
@@ -17081,7 +17092,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
@@ -17123,7 +17134,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" s="13" t="n">
@@ -17169,7 +17180,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
@@ -17211,7 +17222,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" s="13" t="n">
@@ -17261,7 +17272,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
@@ -17303,7 +17314,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" s="13" t="n">
@@ -17349,7 +17360,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
@@ -17391,7 +17402,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" s="13" t="n">
@@ -17433,7 +17444,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
@@ -17475,7 +17486,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" s="13" t="n">
@@ -17525,7 +17536,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
@@ -17571,7 +17582,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D25" s="13" t="n">
@@ -17621,7 +17632,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
@@ -17667,7 +17678,7 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D27" s="13" t="n"/>
@@ -17703,7 +17714,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
@@ -17749,7 +17760,7 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" s="13" t="n">
@@ -17795,7 +17806,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
@@ -17837,7 +17848,7 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D31" s="13" t="n">
@@ -17887,7 +17898,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D32" s="11" t="n">
@@ -19156,6 +19167,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -20323,6 +20335,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -21393,6 +21406,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -22695,6 +22709,7 @@
       </c>
       <c r="L32" s="7" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -23963,6 +23978,7 @@
       <c r="K32" s="7" t="inlineStr"/>
       <c r="L32" s="7" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -24062,7 +24078,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -24107,7 +24123,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -24152,7 +24168,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -24197,7 +24213,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -24242,7 +24258,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -24287,7 +24303,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -24332,7 +24348,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -24377,7 +24393,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -24422,7 +24438,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -24458,7 +24474,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -24503,7 +24519,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -24548,7 +24564,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -24593,7 +24609,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -24638,7 +24654,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -24678,7 +24694,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -24723,7 +24739,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -24768,7 +24784,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -24813,7 +24829,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -24858,7 +24874,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -24903,7 +24919,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -24948,7 +24964,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -24993,7 +25009,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -25038,7 +25054,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -25083,7 +25099,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -25128,7 +25144,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -25173,7 +25189,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -25200,7 +25216,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -25245,7 +25261,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -25290,7 +25306,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -25335,7 +25351,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -25380,7 +25396,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -25412,6 +25428,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -25508,7 +25525,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -25553,7 +25570,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -25598,7 +25615,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -25643,7 +25660,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -25688,7 +25705,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -25733,7 +25750,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -25778,7 +25795,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -25823,7 +25840,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -25868,7 +25885,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -25913,7 +25930,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -25958,7 +25975,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -26003,7 +26020,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -26048,7 +26065,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -26093,7 +26110,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -26138,7 +26155,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -26183,7 +26200,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -26228,7 +26245,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -26273,7 +26290,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -26318,7 +26335,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -26363,7 +26380,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -26408,7 +26425,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -26453,7 +26470,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -26498,7 +26515,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -26543,7 +26560,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -26588,7 +26605,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -26633,7 +26650,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -26666,7 +26683,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -26711,7 +26728,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -26756,7 +26773,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -26801,7 +26818,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -26846,7 +26863,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -26878,6 +26895,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -29653,6 +29671,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -29728,7 +29747,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -29768,7 +29787,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -29808,7 +29827,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -29848,7 +29867,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -29893,7 +29912,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -29933,7 +29952,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -29973,7 +29992,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -30013,7 +30032,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -30053,7 +30072,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -30093,7 +30112,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -30138,7 +30157,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -30178,7 +30197,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -30223,7 +30242,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -30268,7 +30287,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -30313,7 +30332,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -30358,7 +30377,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -30403,7 +30422,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -30448,7 +30467,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -30493,7 +30512,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -30538,7 +30557,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -30583,7 +30602,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -30625,7 +30644,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -30670,7 +30689,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -30706,7 +30725,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -30742,7 +30761,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -30778,7 +30797,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -39247,6 +39266,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -39322,7 +39342,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -39358,7 +39378,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -39394,7 +39414,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -39430,7 +39450,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -39461,7 +39481,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -39492,7 +39512,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -39528,7 +39548,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -39564,7 +39584,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -39600,7 +39620,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -39631,7 +39651,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -39662,7 +39682,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -39693,7 +39713,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -39724,7 +39744,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -39755,7 +39775,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -39786,7 +39806,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -39817,7 +39837,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -39848,7 +39868,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -39884,7 +39904,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -39920,7 +39940,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -39956,7 +39976,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -39987,7 +40007,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -40023,7 +40043,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -40059,7 +40079,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -40095,7 +40115,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -40126,7 +40146,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -40162,7 +40182,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -40201,6 +40221,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -40276,7 +40297,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -40321,7 +40342,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -40366,7 +40387,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -40411,7 +40432,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -40456,7 +40477,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -40501,7 +40522,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -40546,7 +40567,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -40591,7 +40612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -40636,7 +40657,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -40681,7 +40702,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -40717,7 +40738,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -40762,7 +40783,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -40807,7 +40828,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -40852,7 +40873,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -40897,7 +40918,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -40942,7 +40963,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -40987,7 +41008,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -41032,7 +41053,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -41077,7 +41098,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -41122,7 +41143,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -41167,7 +41188,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -41203,7 +41224,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -41239,7 +41260,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -41284,7 +41305,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -41329,7 +41350,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -41365,7 +41386,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -41403,6 +41424,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -41478,7 +41500,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -41523,7 +41545,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -41556,7 +41578,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -41601,7 +41623,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -41646,7 +41668,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -41691,7 +41713,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -41736,7 +41758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -41781,7 +41803,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -41826,7 +41848,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -41871,7 +41893,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -41916,7 +41938,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -41961,7 +41983,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -42006,7 +42028,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -42051,7 +42073,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -42096,7 +42118,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -42141,7 +42163,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -42186,7 +42208,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -42231,7 +42253,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -42276,7 +42298,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -42321,7 +42343,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -42363,7 +42385,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -42408,7 +42430,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -42453,7 +42475,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -42498,7 +42520,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -42616,7 +42638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -42656,7 +42678,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -42696,7 +42718,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -42736,7 +42758,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -42776,7 +42798,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -42821,7 +42843,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -42866,7 +42888,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -42911,7 +42933,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -42956,7 +42978,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -43001,7 +43023,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -43046,7 +43068,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -43091,7 +43113,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -43136,7 +43158,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -43181,7 +43203,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -43226,7 +43248,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -43271,7 +43293,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -43316,7 +43338,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -43361,7 +43383,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -43406,7 +43428,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -43451,7 +43473,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -43496,7 +43518,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -43541,7 +43563,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -43586,7 +43608,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -43631,7 +43653,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -43658,7 +43680,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -43685,7 +43707,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -43712,7 +43734,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -43819,7 +43841,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -43855,7 +43877,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -43891,7 +43913,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -43927,7 +43949,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -43963,7 +43985,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -43990,7 +44012,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -44017,7 +44039,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -44053,7 +44075,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -44083,7 +44105,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -44119,7 +44141,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -44155,7 +44177,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -44191,7 +44213,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -44227,7 +44249,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -44260,7 +44282,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -44296,7 +44318,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -44323,7 +44345,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -44359,7 +44381,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -44395,7 +44417,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -44431,7 +44453,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -44467,7 +44489,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -44503,7 +44525,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -44539,7 +44561,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -44575,7 +44597,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -44611,7 +44633,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -44647,7 +44669,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -44683,7 +44705,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -44806,7 +44828,7 @@
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D2" s="20" t="n">
@@ -44852,7 +44874,7 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" s="20" t="n">
@@ -44898,7 +44920,7 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>门将</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" s="20" t="n">
@@ -44944,7 +44966,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D5" s="20" t="n">
@@ -44990,7 +45012,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" s="20" t="n">
@@ -45036,7 +45058,7 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" s="20" t="n">
@@ -45082,7 +45104,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" s="20" t="n">
@@ -45128,7 +45150,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" s="20" t="n">
@@ -45174,7 +45196,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" s="20" t="n">
@@ -45220,7 +45242,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D11" s="20" t="n">
@@ -45266,7 +45288,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D12" s="20" t="n">
@@ -45312,7 +45334,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" s="20" t="n">
@@ -45358,7 +45380,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" s="20" t="n">
@@ -45400,7 +45422,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D15" s="20" t="n">
@@ -45446,7 +45468,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -45482,7 +45504,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" s="20" t="n">
@@ -45528,7 +45550,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D18" s="24" t="n">
@@ -45574,7 +45596,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D19" s="24" t="n">
@@ -45620,7 +45642,7 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D20" s="24" t="n">
@@ -45666,7 +45688,7 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>后卫</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D21" s="24" t="n">
@@ -45712,7 +45734,7 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" s="24" t="n">
@@ -45758,7 +45780,7 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>中场</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" s="20" t="n">
@@ -45804,7 +45826,7 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D24" s="20" t="n">
@@ -45850,7 +45872,7 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D25" s="20" t="n">
@@ -45896,7 +45918,7 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D26" s="20" t="n">
@@ -45942,7 +45964,7 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" s="24" t="n">
@@ -45988,7 +46010,7 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>前锋</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D28" s="20" t="n">

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -40,6 +40,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.7" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1361,7 +1362,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -1373,7 +1374,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -3814,7 +3814,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -5171,7 +5170,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -5198,7 +5196,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -6303,7 +6301,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -7609,7 +7606,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -8889,7 +8885,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -9756,7 +9751,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -10753,7 +10747,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -12390,7 +12384,6 @@
       </c>
       <c r="L32" s="15" t="inlineStr"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -13951,7 +13944,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -15222,7 +15214,6 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -15245,7 +15236,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -15257,7 +15248,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -16472,7 +16462,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19167,7 +19157,6 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -19190,7 +19179,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -20335,7 +20324,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -21406,7 +21394,6 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -22709,7 +22696,6 @@
       </c>
       <c r="L32" s="7" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -23978,7 +23964,6 @@
       <c r="K32" s="7" t="inlineStr"/>
       <c r="L32" s="7" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -25428,7 +25413,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -26895,7 +26879,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -29659,7 +29642,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -29671,7 +29654,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -32156,7 +32138,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33158,7 +33140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34356,8 +34338,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:AQ36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -34600,6 +34582,11 @@
           <t>8/8</t>
         </is>
       </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>8/9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34713,6 +34700,9 @@
       <c r="AP4" t="n">
         <v>43</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34826,6 +34816,9 @@
       <c r="AP5" t="n">
         <v>43</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34942,6 +34935,9 @@
       <c r="AP6" t="n">
         <v>43</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35055,6 +35051,9 @@
       <c r="AP7" t="n">
         <v>43</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35168,6 +35167,9 @@
       <c r="AP8" t="n">
         <v>43</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35269,6 +35271,9 @@
       <c r="AP9" t="n">
         <v>43</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35385,6 +35390,9 @@
       <c r="AP10" t="n">
         <v>43</v>
       </c>
+      <c r="AQ10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35501,6 +35509,9 @@
       <c r="AP11" t="n">
         <v>43</v>
       </c>
+      <c r="AQ11" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35617,6 +35628,9 @@
       <c r="AP12" t="n">
         <v>43</v>
       </c>
+      <c r="AQ12" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35730,6 +35744,9 @@
       <c r="AP13" t="n">
         <v>43</v>
       </c>
+      <c r="AQ13" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35825,6 +35842,9 @@
       <c r="AP14" t="n">
         <v>43</v>
       </c>
+      <c r="AQ14" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35929,6 +35949,9 @@
       <c r="AP15" t="n">
         <v>43</v>
       </c>
+      <c r="AQ15" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36002,6 +36025,9 @@
       <c r="AP16" t="n">
         <v>0</v>
       </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36115,6 +36141,9 @@
       <c r="AP17" t="n">
         <v>43</v>
       </c>
+      <c r="AQ17" t="n">
+        <v>672</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36228,6 +36257,9 @@
       <c r="AP18" t="n">
         <v>43</v>
       </c>
+      <c r="AQ18" t="n">
+        <v>440</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36341,6 +36373,9 @@
       <c r="AP19" t="n">
         <v>43</v>
       </c>
+      <c r="AQ19" t="n">
+        <v>760</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -36451,6 +36486,9 @@
       <c r="AP20" t="n">
         <v>0</v>
       </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -36567,6 +36605,9 @@
       <c r="AP21" t="n">
         <v>43</v>
       </c>
+      <c r="AQ21" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36683,6 +36724,9 @@
       <c r="AP22" t="n">
         <v>43</v>
       </c>
+      <c r="AQ22" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -36787,6 +36831,9 @@
       <c r="AP23" t="n">
         <v>0</v>
       </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -36876,6 +36923,9 @@
       <c r="AP24" t="n">
         <v>0</v>
       </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -36946,6 +36996,9 @@
       <c r="AP25" t="n">
         <v>0</v>
       </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -37031,6 +37084,9 @@
       <c r="AP26" t="n">
         <v>43</v>
       </c>
+      <c r="AQ26" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37144,6 +37200,9 @@
       <c r="AP27" t="n">
         <v>43</v>
       </c>
+      <c r="AQ27" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -37257,6 +37316,9 @@
       <c r="AP28" t="n">
         <v>43</v>
       </c>
+      <c r="AQ28" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -37370,6 +37432,9 @@
       <c r="AP29" t="n">
         <v>43</v>
       </c>
+      <c r="AQ29" t="n">
+        <v>855</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -37483,6 +37548,9 @@
       <c r="AP30" t="n">
         <v>43</v>
       </c>
+      <c r="AQ30" t="n">
+        <v>320</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -37651,6 +37719,9 @@
       <c r="AP32" t="n">
         <v>43</v>
       </c>
+      <c r="AQ32" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -37775,6 +37846,9 @@
       <c r="AP33" t="n">
         <v>0</v>
       </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -37894,6 +37968,9 @@
         <v>72</v>
       </c>
       <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39234,13 +39311,1263 @@
         <v>172</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>8/8 MD-1 · 23人参训·总sRPE=3010 · 明天客vs长春喜都</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>训练内容</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>恢复建议</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J2" t="n">
+        <v>760</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>95</v>
+      </c>
+      <c r="J3" t="n">
+        <v>760</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84</v>
+      </c>
+      <c r="J4" t="n">
+        <v>672</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>首发84'↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>95</v>
+      </c>
+      <c r="J5" t="n">
+        <v>950</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>首发全场·RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>760</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>95</v>
+      </c>
+      <c r="J7" t="n">
+        <v>760</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>440</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>首发55'↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>950</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>首发全场·RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>855</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>855</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>首发全场</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>855</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>首发全场·⚽</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="n">
+        <v>320</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>55'↑·⚽</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>66</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>84'↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>45</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>45</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>45</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>45</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" t="n">
+        <v>45</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>替补未登场·热身15min</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>替补未登场</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>未进名单</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>未进名单·脚趾肿</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>未进名单</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>未进名单·单独训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8/9 ⚽客2-1长春喜都 · 13人上场·总sRPE=9528 · 帕尔曼江⚽+阿西江⚽</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -39254,7 +40581,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -39266,7 +40593,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -40208,7 +41534,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -40221,7 +41547,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -41412,7 +42737,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -41424,7 +42749,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -42555,7 +43879,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -43760,7 +45084,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -44740,7 +46064,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -1362,7 +1362,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -2511,7 +2511,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5196,7 +5196,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10747,7 +10747,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -15236,7 +15236,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -16462,7 +16462,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19179,7 +19179,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -29642,7 +29642,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -32138,7 +32138,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33140,7 +33140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34339,7 +34339,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AQ36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -39410,9 +39410,15 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39427,10 +39433,9 @@
       <c r="J2" t="n">
         <v>760</v>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>首发全场</t>
+          <t>首发全场 | 赛前:脚踝痛</t>
         </is>
       </c>
     </row>
@@ -39450,9 +39455,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39467,7 +39478,6 @@
       <c r="J3" t="n">
         <v>760</v>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>首发全场</t>
@@ -39490,9 +39500,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39507,7 +39523,6 @@
       <c r="J4" t="n">
         <v>672</v>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>首发84'↓</t>
@@ -39530,9 +39545,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39547,7 +39568,6 @@
       <c r="J5" t="n">
         <v>950</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>首发全场·RPE=10</t>
@@ -39570,9 +39590,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39587,7 +39613,6 @@
       <c r="J6" t="n">
         <v>760</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>首发全场</t>
@@ -39610,9 +39635,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39627,7 +39658,6 @@
       <c r="J7" t="n">
         <v>760</v>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>首发全场</t>
@@ -39650,9 +39680,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39667,7 +39703,6 @@
       <c r="J8" t="n">
         <v>440</v>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>首发55'↓</t>
@@ -39690,9 +39725,15 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39707,10 +39748,9 @@
       <c r="J9" t="n">
         <v>950</v>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>首发全场·RPE=10</t>
+          <t>首发全场·RPE=10 | 赛前:内侧副韧带有点疼</t>
         </is>
       </c>
     </row>
@@ -39730,9 +39770,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39747,7 +39793,6 @@
       <c r="J10" t="n">
         <v>855</v>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>首发全场</t>
@@ -39770,9 +39815,15 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39787,7 +39838,6 @@
       <c r="J11" t="n">
         <v>855</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>首发全场</t>
@@ -39810,9 +39860,15 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39827,7 +39883,6 @@
       <c r="J12" t="n">
         <v>855</v>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>首发全场·⚽</t>
@@ -39850,9 +39905,15 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39867,7 +39928,6 @@
       <c r="J13" t="n">
         <v>320</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>55'↑·⚽</t>
@@ -39890,9 +39950,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>中乙第18轮 客vs长春喜都 2-1胜 5-4-1 95min</t>
@@ -39907,7 +39973,6 @@
       <c r="J14" t="n">
         <v>66</v>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>84'↑</t>
@@ -39930,9 +39995,15 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -39947,10 +40018,9 @@
       <c r="J15" t="n">
         <v>60</v>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>替补未登场</t>
+          <t>替补未登场 | 赛前:腰疼</t>
         </is>
       </c>
     </row>
@@ -39970,9 +40040,15 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -39987,7 +40063,6 @@
       <c r="J16" t="n">
         <v>60</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40010,9 +40085,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40027,10 +40108,9 @@
       <c r="J17" t="n">
         <v>45</v>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>替补未登场</t>
+          <t>替补未登场 | 赛前:左膝</t>
         </is>
       </c>
     </row>
@@ -40050,9 +40130,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40067,7 +40153,6 @@
       <c r="J18" t="n">
         <v>45</v>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40090,9 +40175,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40107,7 +40198,6 @@
       <c r="J19" t="n">
         <v>60</v>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40130,9 +40220,15 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40147,7 +40243,6 @@
       <c r="J20" t="n">
         <v>60</v>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40170,9 +40265,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40187,7 +40288,6 @@
       <c r="J21" t="n">
         <v>45</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40210,9 +40310,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40227,7 +40333,6 @@
       <c r="J22" t="n">
         <v>45</v>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40250,9 +40355,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40267,7 +40378,6 @@
       <c r="J23" t="n">
         <v>45</v>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40290,9 +40400,15 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>替补未登场·热身15min</t>
@@ -40307,7 +40423,6 @@
       <c r="J24" t="n">
         <v>60</v>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>替补未登场</t>
@@ -40330,9 +40445,15 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>未进名单</t>
@@ -40341,10 +40462,9 @@
       <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>未进名单·脚趾肿</t>
+          <t>未进名单·脚趾肿 | 赛前:脚趾头肿</t>
         </is>
       </c>
     </row>
@@ -40364,9 +40484,12 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>未进名单</t>
@@ -40375,7 +40498,6 @@
       <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>未进名单·单独训练</t>
@@ -40398,15 +40520,11 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>未随队</t>
@@ -40429,15 +40547,11 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>未随队</t>
@@ -40460,15 +40574,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>未随队</t>
@@ -40491,15 +40601,11 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>未随队</t>
@@ -40522,52 +40628,24 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>未随队</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>8/9 ⚽客2-1长春喜都 · 13人上场·总sRPE=9528 · 帕尔曼江⚽+阿西江⚽</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40581,7 +40659,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -41534,7 +41612,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -42737,7 +42815,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -43879,7 +43957,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -45084,7 +45162,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -46064,7 +46142,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -41,6 +41,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACWR负荷比" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1362,7 +1363,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -2511,7 +2512,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5196,7 +5197,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10747,7 +10748,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -15236,7 +15237,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -16462,7 +16463,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19179,7 +19180,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -29642,7 +29643,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -32138,7 +32139,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33140,7 +33141,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34338,8 +34339,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:AW36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -34587,6 +34588,11 @@
           <t>8/9</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>8/11</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34703,6 +34709,9 @@
       <c r="AQ4" t="n">
         <v>760</v>
       </c>
+      <c r="AR4" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34819,6 +34828,9 @@
       <c r="AQ5" t="n">
         <v>60</v>
       </c>
+      <c r="AR5" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34938,6 +34950,9 @@
       <c r="AQ6" t="n">
         <v>60</v>
       </c>
+      <c r="AR6" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35054,6 +35069,9 @@
       <c r="AQ7" t="n">
         <v>950</v>
       </c>
+      <c r="AR7" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35170,6 +35188,9 @@
       <c r="AQ8" t="n">
         <v>760</v>
       </c>
+      <c r="AR8" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35274,6 +35295,9 @@
       <c r="AQ9" t="n">
         <v>66</v>
       </c>
+      <c r="AR9" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35393,6 +35417,9 @@
       <c r="AQ10" t="n">
         <v>60</v>
       </c>
+      <c r="AR10" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35631,6 +35658,9 @@
       <c r="AQ12" t="n">
         <v>45</v>
       </c>
+      <c r="AR12" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35747,6 +35777,9 @@
       <c r="AQ13" t="n">
         <v>760</v>
       </c>
+      <c r="AR13" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35845,6 +35878,9 @@
       <c r="AQ14" t="n">
         <v>855</v>
       </c>
+      <c r="AR14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35952,6 +35988,9 @@
       <c r="AQ15" t="n">
         <v>45</v>
       </c>
+      <c r="AR15" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36028,6 +36067,9 @@
       <c r="AQ16" t="n">
         <v>0</v>
       </c>
+      <c r="AR16" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36144,6 +36186,9 @@
       <c r="AQ17" t="n">
         <v>672</v>
       </c>
+      <c r="AR17" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36260,6 +36305,9 @@
       <c r="AQ18" t="n">
         <v>440</v>
       </c>
+      <c r="AR18" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36376,6 +36424,9 @@
       <c r="AQ19" t="n">
         <v>760</v>
       </c>
+      <c r="AR19" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -36608,6 +36659,9 @@
       <c r="AQ21" t="n">
         <v>45</v>
       </c>
+      <c r="AR21" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36727,6 +36781,9 @@
       <c r="AQ22" t="n">
         <v>45</v>
       </c>
+      <c r="AR22" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -36834,6 +36891,9 @@
       <c r="AQ23" t="n">
         <v>0</v>
       </c>
+      <c r="AR23" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -36926,6 +36986,9 @@
       <c r="AQ24" t="n">
         <v>0</v>
       </c>
+      <c r="AR24" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37087,6 +37150,9 @@
       <c r="AQ26" t="n">
         <v>45</v>
       </c>
+      <c r="AR26" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37203,6 +37269,9 @@
       <c r="AQ27" t="n">
         <v>855</v>
       </c>
+      <c r="AR27" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -37319,6 +37388,9 @@
       <c r="AQ28" t="n">
         <v>950</v>
       </c>
+      <c r="AR28" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -37435,6 +37507,9 @@
       <c r="AQ29" t="n">
         <v>855</v>
       </c>
+      <c r="AR29" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -37551,6 +37626,9 @@
       <c r="AQ30" t="n">
         <v>320</v>
       </c>
+      <c r="AR30" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -37722,6 +37800,9 @@
       <c r="AQ32" t="n">
         <v>60</v>
       </c>
+      <c r="AR32" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -37849,6 +37930,9 @@
       <c r="AQ33" t="n">
         <v>0</v>
       </c>
+      <c r="AR33" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -37972,6 +38056,9 @@
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="35">
@@ -40639,13 +40726,1393 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>8/9 ⚽客2-1长春喜都 · 13人上场·总sRPE=9528 · 帕尔曼江⚽+阿西江⚽</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>训练内容</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>恢复建议</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>左腿后群有点反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>内收肌紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="n">
+        <v>120</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>180</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" t="n">
+        <v>180</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
+        <v>120</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" t="n">
+        <v>180</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>小腿酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" t="n">
+        <v>180</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" t="n">
+        <v>120</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" t="n">
+        <v>180</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>脚腕微痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" t="n">
+        <v>180</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" t="n">
+        <v>120</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" t="n">
+        <v>180</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" t="n">
+        <v>120</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" t="n">
+        <v>120</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>120</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" t="n">
+        <v>180</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>左膝盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" t="n">
+        <v>120</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>60</v>
+      </c>
+      <c r="J23" t="n">
+        <v>180</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J25" t="n">
+        <v>300</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RPE=5偏高·赛前MCL疼⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" t="n">
+        <v>180</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" t="n">
+        <v>120</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>60</v>
+      </c>
+      <c r="J28" t="n">
+        <v>120</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>脚趾头肿</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8/11 D+2 · 27人参训·总sRPE=4140 · 丁云峰左腿后群反应🆕·何麟立内收肌紧·张辉脚腕微痛🆕</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40659,7 +42126,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -41612,7 +43079,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -42815,7 +44282,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -43957,7 +45424,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -45162,7 +46629,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -46142,7 +47609,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="22" activeTab="32" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="22" activeTab="36" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.8" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1363,7 +1364,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -2512,7 +2513,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5197,7 +5198,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10748,7 +10749,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -15237,7 +15238,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -16463,7 +16464,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19180,7 +19181,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -29643,7 +29644,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -32139,7 +32140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33141,7 +33142,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34339,8 +34340,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <dimension ref="A1:AS36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -34593,6 +34594,11 @@
           <t>8/11</t>
         </is>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>8/12</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34712,6 +34718,9 @@
       <c r="AR4" t="n">
         <v>180</v>
       </c>
+      <c r="AS4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34831,6 +34840,9 @@
       <c r="AR5" t="n">
         <v>120</v>
       </c>
+      <c r="AS5" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34953,6 +34965,9 @@
       <c r="AR6" t="n">
         <v>120</v>
       </c>
+      <c r="AS6" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35072,6 +35087,9 @@
       <c r="AR7" t="n">
         <v>180</v>
       </c>
+      <c r="AS7" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35191,6 +35209,9 @@
       <c r="AR8" t="n">
         <v>120</v>
       </c>
+      <c r="AS8" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35298,6 +35319,9 @@
       <c r="AR9" t="n">
         <v>120</v>
       </c>
+      <c r="AS9" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35420,6 +35444,9 @@
       <c r="AR10" t="n">
         <v>120</v>
       </c>
+      <c r="AS10" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35539,6 +35566,9 @@
       <c r="AQ11" t="n">
         <v>60</v>
       </c>
+      <c r="AS11" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35661,6 +35691,9 @@
       <c r="AR12" t="n">
         <v>180</v>
       </c>
+      <c r="AS12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35780,6 +35813,9 @@
       <c r="AR13" t="n">
         <v>180</v>
       </c>
+      <c r="AS13" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35881,6 +35917,9 @@
       <c r="AR14" t="n">
         <v>180</v>
       </c>
+      <c r="AS14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35991,6 +36030,9 @@
       <c r="AR15" t="n">
         <v>180</v>
       </c>
+      <c r="AS15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36070,6 +36112,9 @@
       <c r="AR16" t="n">
         <v>180</v>
       </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36189,6 +36234,9 @@
       <c r="AR17" t="n">
         <v>120</v>
       </c>
+      <c r="AS17" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36308,6 +36356,9 @@
       <c r="AR18" t="n">
         <v>120</v>
       </c>
+      <c r="AS18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36427,6 +36478,9 @@
       <c r="AR19" t="n">
         <v>120</v>
       </c>
+      <c r="AS19" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -36540,6 +36594,9 @@
       <c r="AQ20" t="n">
         <v>0</v>
       </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -36662,6 +36719,9 @@
       <c r="AR21" t="n">
         <v>120</v>
       </c>
+      <c r="AS21" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36784,6 +36844,9 @@
       <c r="AR22" t="n">
         <v>120</v>
       </c>
+      <c r="AS22" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -36894,6 +36957,9 @@
       <c r="AR23" t="n">
         <v>120</v>
       </c>
+      <c r="AS23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -36989,6 +37055,9 @@
       <c r="AR24" t="n">
         <v>180</v>
       </c>
+      <c r="AS24" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37062,6 +37131,9 @@
       <c r="AQ25" t="n">
         <v>0</v>
       </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -37153,6 +37225,9 @@
       <c r="AR26" t="n">
         <v>120</v>
       </c>
+      <c r="AS26" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37272,6 +37347,9 @@
       <c r="AR27" t="n">
         <v>120</v>
       </c>
+      <c r="AS27" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -37391,6 +37469,9 @@
       <c r="AR28" t="n">
         <v>300</v>
       </c>
+      <c r="AS28" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -37510,6 +37591,9 @@
       <c r="AR29" t="n">
         <v>180</v>
       </c>
+      <c r="AS29" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -37629,6 +37713,9 @@
       <c r="AR30" t="n">
         <v>180</v>
       </c>
+      <c r="AS30" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -37803,6 +37890,9 @@
       <c r="AR32" t="n">
         <v>180</v>
       </c>
+      <c r="AS32" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -37933,6 +38023,9 @@
       <c r="AR33" t="n">
         <v>180</v>
       </c>
+      <c r="AS33" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -38059,6 +38152,9 @@
       </c>
       <c r="AR34" t="n">
         <v>120</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -40848,77 +40944,1379 @@
       <c r="J2" t="n">
         <v>180</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>左腿后群有点反应</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J3" t="n">
+        <v>120</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>内收肌紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="J4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="J6" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="J7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" t="n">
+        <v>180</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>小腿酸痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="J11" t="n">
+        <v>180</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>紧</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J12" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" t="n">
+        <v>180</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" t="n">
+        <v>120</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>脚腕微痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" t="n">
+        <v>120</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="J21" t="n">
+        <v>180</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>左膝盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>60</v>
+      </c>
+      <c r="J23" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J25" t="n">
+        <v>300</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>RPE=5偏高·赛前MCL疼⚠️</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>60</v>
+      </c>
+      <c r="J27" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>60</v>
+      </c>
+      <c r="J28" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>脚趾头肿</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>未参加</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8/11 D+2 · 27人参训·总sRPE=4140 · 丁云峰左腿后群反应🆕·何麟立内收肌紧·张辉脚腕微痛🆕</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>训练内容</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>恢复建议</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>左腿后群有点反应</t>
+          <t>脚踝疼</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>何麟立</t>
+          <t>杨卓燠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>内收肌紧</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>凌中阳</t>
+          <t>王款(U21)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -40928,17 +42326,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J4" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -40946,17 +42344,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>刘子洁</t>
+          <t>王熙博</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -40970,17 +42368,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -40988,17 +42386,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>努尔扎提-努尔兰</t>
+          <t>张俊哲</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -41012,35 +42410,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>正常一些</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>吕佳骏</t>
+          <t>张天龙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -41054,17 +42456,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -41072,41 +42474,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>巫林峰</t>
+          <t>凌中阳</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -41114,17 +42516,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>布格拉汗-斯坎旦尔</t>
+          <t>陈少豪</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -41138,17 +42540,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -41156,58 +42558,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>帕尔曼江-克尤木</t>
+          <t>李金羽</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>小腿酸痛</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>张俊哲</t>
+          <t>王捷(U21)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -41216,44 +42614,44 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J11" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>紧</t>
+          <t>左膝</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>张天龙</t>
+          <t>王皓文(U21)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -41262,27 +42660,27 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -41290,155 +42688,140 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>张海轩</t>
+          <t>丁云峰</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>脚踝痛</t>
+          <t>睡眠偏高</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>张辉</t>
+          <t>杨文杰</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>脚腕微痛</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>朱云天(U21)</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" t="n">
-        <v>60</v>
-      </c>
-      <c r="J15" t="n">
-        <v>180</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>未参训</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>杨卓燠</t>
+          <t>何麟立</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -41448,63 +42831,63 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J16" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>腰疼</t>
+          <t>内收肌还是有点紧</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>杨文杰</t>
+          <t>布格拉汗-斯坎旦尔</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J17" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -41512,12 +42895,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>杨翼璇</t>
+          <t>巫林峰</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -41536,17 +42919,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -41554,12 +42937,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>林楷轩(U21)</t>
+          <t>张辉</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -41568,7 +42951,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -41578,17 +42961,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J19" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -41596,12 +42979,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>栾昊(U21)</t>
+          <t>谢锦政</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -41610,7 +42993,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -41618,83 +43001,72 @@
       <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" t="n">
-        <v>120</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>脚趾恢复中</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>王捷(U21)</t>
+          <t>栾昊(U21)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J21" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>左膝盖</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>王款(U21)</t>
+          <t>杨翼璇</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -41708,17 +43080,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J22" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -41726,17 +43098,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>王熙博</t>
+          <t>林楷轩(U21)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -41746,21 +43118,21 @@
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J23" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -41768,41 +43140,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>王皓文(U21)</t>
+          <t>朱云天(U21)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J24" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -41810,87 +43182,66 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>艾沙江-库尔班</t>
+          <t>董德</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>60</v>
-      </c>
-      <c r="J25" t="n">
-        <v>300</v>
-      </c>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>RPE=5偏高·赛前MCL疼⚠️</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>阿西江-白山</t>
+          <t>吕佳骏</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>MID</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -41898,17 +43249,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>陈少豪</t>
+          <t>陈祥煜</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -41922,17 +43273,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J27" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -41940,12 +43291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陈祥煜</t>
+          <t>艾沙江-库尔班</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -41957,24 +43308,24 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>D+2恢复·慢跑12'+拉伸8'+颠球+井字棋+头球+慢跑10'·60'</t>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J28" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -41982,69 +43333,83 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>谢锦政</t>
+          <t>帕尔曼江-克尤木</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未参加</t>
-        </is>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>50</v>
+      </c>
+      <c r="J29" t="n">
+        <v>200</v>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>脚趾头肿</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>李金羽</t>
+          <t>阿西江-白山</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DEF</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未参加</t>
-        </is>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>50</v>
+      </c>
+      <c r="J30" t="n">
+        <v>200</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -42052,67 +43417,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>董德</t>
+          <t>努尔扎提-努尔兰</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>FWD</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未参加</t>
-        </is>
+          <t>MD-3·热身5'+抢圈7'+头球6'+战术15'+定位球10'·50'</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>50</v>
+      </c>
+      <c r="J31" t="n">
+        <v>200</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>8/11 D+2 · 27人参训·总sRPE=4140 · 丁云峰左腿后群反应🆕·何麟立内收肌紧·张辉脚腕微痛🆕</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -42126,7 +43468,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -43079,7 +44421,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -44282,7 +45624,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -45424,7 +46766,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -46629,7 +47971,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -47609,7 +48951,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -1364,7 +1364,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -2513,7 +2513,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5198,7 +5198,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10749,7 +10749,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -15238,7 +15238,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -16464,7 +16464,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19181,7 +19181,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -29644,7 +29644,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -32140,7 +32140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33142,7 +33142,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34341,7 +34341,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AS36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -36113,7 +36113,7 @@
         <v>180</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -38154,7 +38154,7 @@
         <v>120</v>
       </c>
       <c r="AS34" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35">
@@ -42250,7 +42250,6 @@
       <c r="J2" t="n">
         <v>100</v>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>脚踝疼</t>
@@ -42296,8 +42295,6 @@
       <c r="J3" t="n">
         <v>150</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42338,8 +42335,6 @@
       <c r="J4" t="n">
         <v>150</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42380,8 +42375,6 @@
       <c r="J5" t="n">
         <v>100</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42422,7 +42415,6 @@
       <c r="J6" t="n">
         <v>150</v>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>正常一些</t>
@@ -42468,8 +42460,6 @@
       <c r="J7" t="n">
         <v>200</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42510,8 +42500,6 @@
       <c r="J8" t="n">
         <v>200</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42552,8 +42540,6 @@
       <c r="J9" t="n">
         <v>150</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42594,8 +42580,6 @@
       <c r="J10" t="n">
         <v>150</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -42636,7 +42620,6 @@
       <c r="J11" t="n">
         <v>150</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>左膝</t>
@@ -42682,8 +42665,6 @@
       <c r="J12" t="n">
         <v>250</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -42724,7 +42705,6 @@
       <c r="J13" t="n">
         <v>150</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>睡眠偏高</t>
@@ -42770,8 +42750,11 @@
       <c r="J14" t="n">
         <v>150</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42792,15 +42775,28 @@
       <c r="D15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MD-3·单练(未参加比赛环节)·50'</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>未参训</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
         </is>
       </c>
     </row>
@@ -42843,7 +42839,6 @@
       <c r="J16" t="n">
         <v>250</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>内收肌还是有点紧</t>
@@ -42889,8 +42884,6 @@
       <c r="J17" t="n">
         <v>200</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42931,8 +42924,6 @@
       <c r="J18" t="n">
         <v>150</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42973,8 +42964,6 @@
       <c r="J19" t="n">
         <v>300</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43001,10 +42990,6 @@
       <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>脚趾恢复中</t>
@@ -43050,8 +43035,6 @@
       <c r="J21" t="n">
         <v>250</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -43092,8 +43075,6 @@
       <c r="J22" t="n">
         <v>150</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -43134,8 +43115,11 @@
       <c r="J23" t="n">
         <v>100</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -43176,8 +43160,11 @@
       <c r="J24" t="n">
         <v>300</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>单练(未参加比赛环节)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -43195,14 +43182,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43235,16 +43214,14 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
         <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>100</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>250</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -43285,8 +43262,6 @@
       <c r="J27" t="n">
         <v>150</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -43327,8 +43302,6 @@
       <c r="J28" t="n">
         <v>250</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -43369,8 +43342,6 @@
       <c r="J29" t="n">
         <v>200</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -43411,8 +43382,6 @@
       <c r="J30" t="n">
         <v>200</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -43453,8 +43422,6 @@
       <c r="J31" t="n">
         <v>200</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43468,7 +43435,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -44421,7 +44388,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -45624,7 +45591,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -46766,7 +46733,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -47971,7 +47938,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -48951,7 +48918,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="22" activeTab="36" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="22" activeTab="37" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.9" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.13" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34340,7 +34341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS36"/>
+  <dimension ref="A1:AT36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
@@ -34599,6 +34600,11 @@
           <t>8/12</t>
         </is>
       </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34721,6 +34727,9 @@
       <c r="AS4" t="n">
         <v>100</v>
       </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34843,6 +34852,9 @@
       <c r="AS5" t="n">
         <v>150</v>
       </c>
+      <c r="AT5" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34968,6 +34980,9 @@
       <c r="AS6" t="n">
         <v>150</v>
       </c>
+      <c r="AT6" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35090,6 +35105,9 @@
       <c r="AS7" t="n">
         <v>150</v>
       </c>
+      <c r="AT7" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35212,6 +35230,9 @@
       <c r="AS8" t="n">
         <v>200</v>
       </c>
+      <c r="AT8" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35322,6 +35343,9 @@
       <c r="AS9" t="n">
         <v>200</v>
       </c>
+      <c r="AT9" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35447,6 +35471,9 @@
       <c r="AS10" t="n">
         <v>150</v>
       </c>
+      <c r="AT10" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35569,6 +35596,9 @@
       <c r="AS11" t="n">
         <v>150</v>
       </c>
+      <c r="AT11" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35694,6 +35724,9 @@
       <c r="AS12" t="n">
         <v>150</v>
       </c>
+      <c r="AT12" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35816,6 +35849,9 @@
       <c r="AS13" t="n">
         <v>250</v>
       </c>
+      <c r="AT13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35920,6 +35956,9 @@
       <c r="AS14" t="n">
         <v>150</v>
       </c>
+      <c r="AT14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36033,6 +36072,9 @@
       <c r="AS15" t="n">
         <v>150</v>
       </c>
+      <c r="AT15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36115,6 +36157,9 @@
       <c r="AS16" t="n">
         <v>100</v>
       </c>
+      <c r="AT16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36237,6 +36282,9 @@
       <c r="AS17" t="n">
         <v>250</v>
       </c>
+      <c r="AT17" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36359,6 +36407,9 @@
       <c r="AS18" t="n">
         <v>150</v>
       </c>
+      <c r="AT18" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36481,6 +36532,9 @@
       <c r="AS19" t="n">
         <v>300</v>
       </c>
+      <c r="AT19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -36597,6 +36651,9 @@
       <c r="AS20" t="n">
         <v>0</v>
       </c>
+      <c r="AT20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -36722,6 +36779,9 @@
       <c r="AS21" t="n">
         <v>250</v>
       </c>
+      <c r="AT21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36847,6 +36907,9 @@
       <c r="AS22" t="n">
         <v>150</v>
       </c>
+      <c r="AT22" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -36960,6 +37023,9 @@
       <c r="AS23" t="n">
         <v>100</v>
       </c>
+      <c r="AT23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -37058,6 +37124,9 @@
       <c r="AS24" t="n">
         <v>300</v>
       </c>
+      <c r="AT24" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37134,6 +37203,9 @@
       <c r="AS25" t="n">
         <v>0</v>
       </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -37228,6 +37300,9 @@
       <c r="AS26" t="n">
         <v>200</v>
       </c>
+      <c r="AT26" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37350,6 +37425,9 @@
       <c r="AS27" t="n">
         <v>150</v>
       </c>
+      <c r="AT27" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -37472,6 +37550,9 @@
       <c r="AS28" t="n">
         <v>250</v>
       </c>
+      <c r="AT28" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -37594,6 +37675,9 @@
       <c r="AS29" t="n">
         <v>200</v>
       </c>
+      <c r="AT29" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -37716,6 +37800,9 @@
       <c r="AS30" t="n">
         <v>200</v>
       </c>
+      <c r="AT30" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -37893,6 +37980,9 @@
       <c r="AS32" t="n">
         <v>200</v>
       </c>
+      <c r="AT32" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -38026,6 +38116,9 @@
       <c r="AS33" t="n">
         <v>100</v>
       </c>
+      <c r="AT33" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -38155,6 +38248,9 @@
       </c>
       <c r="AS34" t="n">
         <v>250</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="35">
@@ -43422,6 +43518,1174 @@
       <c r="J31" t="n">
         <v>200</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>训练内容</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>恢复建议</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" t="n">
+        <v>150</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" t="n">
+        <v>150</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" t="n">
+        <v>150</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J5" t="n">
+        <v>150</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>150</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" t="n">
+        <v>150</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>150</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="n">
+        <v>150</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>150</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J11" t="n">
+        <v>150</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" t="n">
+        <v>150</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>150</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>150</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>单练(黄牌停赛)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J19" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" t="n">
+        <v>150</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>50</v>
+      </c>
+      <c r="J21" t="n">
+        <v>150</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>50</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>50</v>
+      </c>
+      <c r="J24" t="n">
+        <v>150</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J25" t="n">
+        <v>150</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>50</v>
+      </c>
+      <c r="J26" t="n">
+        <v>150</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>50</v>
+      </c>
+      <c r="J27" t="n">
+        <v>150</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J28" t="n">
+        <v>150</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>50</v>
+      </c>
+      <c r="J29" t="n">
+        <v>150</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>脚崴缺席</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -1365,7 +1365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -2514,7 +2514,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5199,7 +5199,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10750,7 +10750,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -15239,7 +15239,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -16465,7 +16465,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19182,7 +19182,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -29645,7 +29645,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -32141,7 +32141,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33143,7 +33143,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34342,7 +34342,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AT36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -43611,9 +43611,6 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43628,8 +43625,6 @@
       <c r="J2" t="n">
         <v>150</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43647,9 +43642,6 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43664,8 +43656,6 @@
       <c r="J3" t="n">
         <v>150</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43683,9 +43673,6 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43700,8 +43687,6 @@
       <c r="J4" t="n">
         <v>150</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43719,9 +43704,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43736,8 +43718,6 @@
       <c r="J5" t="n">
         <v>150</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43755,9 +43735,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43772,8 +43749,6 @@
       <c r="J6" t="n">
         <v>150</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43791,9 +43766,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43808,8 +43780,6 @@
       <c r="J7" t="n">
         <v>150</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43827,9 +43797,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -43844,7 +43811,6 @@
       <c r="J8" t="n">
         <v>150</v>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>单练(未参加战术)</t>
@@ -43867,9 +43833,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43884,8 +43847,6 @@
       <c r="J9" t="n">
         <v>150</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43903,9 +43864,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43920,7 +43878,6 @@
       <c r="J10" t="n">
         <v>150</v>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>左膝</t>
@@ -43943,9 +43900,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43960,8 +43914,6 @@
       <c r="J11" t="n">
         <v>150</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43979,9 +43931,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43996,8 +43945,6 @@
       <c r="J12" t="n">
         <v>150</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -44015,9 +43962,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44032,7 +43976,6 @@
       <c r="J13" t="n">
         <v>100</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>单练(未参加战术)</t>
@@ -44055,9 +43998,6 @@
           <t>DEF</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44072,8 +44012,6 @@
       <c r="J14" t="n">
         <v>100</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -44091,9 +44029,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44108,8 +44043,6 @@
       <c r="J15" t="n">
         <v>150</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -44127,9 +44060,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44144,8 +44074,6 @@
       <c r="J16" t="n">
         <v>150</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44163,9 +44091,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44180,8 +44105,6 @@
       <c r="J17" t="n">
         <v>150</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44199,9 +44122,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44216,7 +44136,6 @@
       <c r="J18" t="n">
         <v>100</v>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>单练(黄牌停赛)</t>
@@ -44239,9 +44158,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44256,7 +44172,6 @@
       <c r="J19" t="n">
         <v>100</v>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>单练(未参加战术)</t>
@@ -44279,12 +44194,9 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+          <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -44296,8 +44208,11 @@
       <c r="J20" t="n">
         <v>150</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>单练(未参加战术)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44315,9 +44230,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44332,8 +44244,6 @@
       <c r="J21" t="n">
         <v>150</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -44351,9 +44261,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44368,7 +44275,6 @@
       <c r="J22" t="n">
         <v>100</v>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>单练(未参加战术)</t>
@@ -44391,9 +44297,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44408,7 +44311,6 @@
       <c r="J23" t="n">
         <v>100</v>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>单练(未参加战术)</t>
@@ -44431,9 +44333,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44448,8 +44347,6 @@
       <c r="J24" t="n">
         <v>150</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -44467,9 +44364,6 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44484,8 +44378,6 @@
       <c r="J25" t="n">
         <v>150</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -44503,9 +44395,6 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44520,8 +44409,6 @@
       <c r="J26" t="n">
         <v>150</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -44539,9 +44426,6 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44556,8 +44440,6 @@
       <c r="J27" t="n">
         <v>150</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -44575,9 +44457,6 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44592,8 +44471,6 @@
       <c r="J28" t="n">
         <v>150</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -44611,9 +44488,6 @@
           <t>FWD</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44628,8 +44502,6 @@
       <c r="J29" t="n">
         <v>150</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -44647,14 +44519,6 @@
           <t>GK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>脚崴缺席</t>
@@ -44677,15 +44541,6 @@
           <t>MID</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -44699,7 +44554,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -45652,7 +45507,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -46855,7 +46710,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -47997,7 +47852,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -49202,7 +49057,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -50182,7 +50037,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -43611,6 +43611,15 @@
           <t>GK</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43642,6 +43651,15 @@
           <t>GK</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43673,6 +43691,15 @@
           <t>GK</t>
         </is>
       </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43704,6 +43731,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43718,6 +43754,11 @@
       <c r="J5" t="n">
         <v>150</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>脚微痛</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43735,6 +43776,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43766,6 +43816,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43797,6 +43856,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -43833,6 +43901,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43864,6 +43941,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43880,7 +43966,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>左膝</t>
+          <t>左膝 左膝盖</t>
         </is>
       </c>
     </row>
@@ -43900,6 +43986,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43931,6 +44026,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -43962,6 +44066,15 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -43998,6 +44111,9 @@
           <t>DEF</t>
         </is>
       </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44029,6 +44145,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44060,6 +44185,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44091,6 +44225,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44122,6 +44265,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44158,6 +44310,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44194,6 +44355,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44230,6 +44400,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44261,6 +44440,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44297,6 +44485,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+单练30'·50'</t>
@@ -44333,6 +44530,15 @@
           <t>MID</t>
         </is>
       </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44364,6 +44570,15 @@
           <t>FWD</t>
         </is>
       </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44395,6 +44610,15 @@
           <t>FWD</t>
         </is>
       </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44409,6 +44633,11 @@
       <c r="J26" t="n">
         <v>150</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>左后群紧</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -44426,6 +44655,15 @@
           <t>FWD</t>
         </is>
       </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44457,6 +44695,15 @@
           <t>FWD</t>
         </is>
       </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44488,6 +44735,15 @@
           <t>FWD</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
@@ -44519,9 +44775,18 @@
           <t>GK</t>
         </is>
       </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>脚崴缺席</t>
+          <t>脚崴缺席 脚踝疼</t>
         </is>
       </c>
     </row>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="22" activeTab="37" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9840" tabRatio="600" firstSheet="22" activeTab="38" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.11" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.12" sheetId="37" state="visible" r:id="rId37"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.13" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.14" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1365,7 +1366,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -2514,7 +2515,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13.2980769230769" customWidth="1" min="1" max="1"/>
   </cols>
@@ -5199,7 +5200,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.3846153846154" customWidth="1" min="1" max="1"/>
     <col width="21.3076923076923" customWidth="1" min="2" max="2"/>
@@ -10750,7 +10751,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="22.5961538461538" customWidth="1" min="7" max="7"/>
     <col width="17.4711538461538" customWidth="1" min="11" max="11"/>
@@ -15239,7 +15240,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -16465,7 +16466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.4903846153846" customWidth="1" min="1" max="1"/>
     <col width="30.5" customWidth="1" min="2" max="2"/>
@@ -19182,7 +19183,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="26.125" customWidth="1" min="1" max="1"/>
     <col width="16.5096153846154" customWidth="1" min="7" max="7"/>
@@ -29645,7 +29646,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -32141,7 +32142,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="18.2692307692308" customWidth="1" min="2" max="2"/>
     <col width="66.81730769230769" customWidth="1" min="7" max="7"/>
@@ -33143,7 +33144,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
     <col width="58.6538461538462" customWidth="1" min="7" max="7"/>
@@ -34341,8 +34342,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:AU36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="41.1826923076923" customWidth="1" min="1" max="1"/>
     <col width="12.6538461538462" customWidth="1" min="2" max="2"/>
@@ -34605,6 +34606,11 @@
           <t>8/13</t>
         </is>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34730,6 +34736,9 @@
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34855,6 +34864,9 @@
       <c r="AT5" t="n">
         <v>150</v>
       </c>
+      <c r="AU5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34983,6 +34995,9 @@
       <c r="AT6" t="n">
         <v>150</v>
       </c>
+      <c r="AU6" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35108,6 +35123,9 @@
       <c r="AT7" t="n">
         <v>150</v>
       </c>
+      <c r="AU7" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35233,6 +35251,9 @@
       <c r="AT8" t="n">
         <v>150</v>
       </c>
+      <c r="AU8" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35346,6 +35367,9 @@
       <c r="AT9" t="n">
         <v>150</v>
       </c>
+      <c r="AU9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35474,6 +35498,9 @@
       <c r="AT10" t="n">
         <v>150</v>
       </c>
+      <c r="AU10" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35599,6 +35626,9 @@
       <c r="AT11" t="n">
         <v>150</v>
       </c>
+      <c r="AU11" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35727,6 +35757,9 @@
       <c r="AT12" t="n">
         <v>150</v>
       </c>
+      <c r="AU12" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35852,6 +35885,9 @@
       <c r="AT13" t="n">
         <v>150</v>
       </c>
+      <c r="AU13" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35959,6 +35995,9 @@
       <c r="AT14" t="n">
         <v>150</v>
       </c>
+      <c r="AU14" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36075,6 +36114,9 @@
       <c r="AT15" t="n">
         <v>100</v>
       </c>
+      <c r="AU15" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -36160,6 +36202,9 @@
       <c r="AT16" t="n">
         <v>100</v>
       </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36285,6 +36330,9 @@
       <c r="AT17" t="n">
         <v>150</v>
       </c>
+      <c r="AU17" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36410,6 +36458,9 @@
       <c r="AT18" t="n">
         <v>150</v>
       </c>
+      <c r="AU18" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -36535,6 +36586,9 @@
       <c r="AT19" t="n">
         <v>100</v>
       </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -36654,6 +36708,9 @@
       <c r="AT20" t="n">
         <v>100</v>
       </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -36782,6 +36839,9 @@
       <c r="AT21" t="n">
         <v>150</v>
       </c>
+      <c r="AU21" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36910,6 +36970,9 @@
       <c r="AT22" t="n">
         <v>150</v>
       </c>
+      <c r="AU22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -37026,6 +37089,9 @@
       <c r="AT23" t="n">
         <v>100</v>
       </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -37127,6 +37193,9 @@
       <c r="AT24" t="n">
         <v>100</v>
       </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -37206,6 +37275,9 @@
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -37303,6 +37375,9 @@
       <c r="AT26" t="n">
         <v>150</v>
       </c>
+      <c r="AU26" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -37428,6 +37503,9 @@
       <c r="AT27" t="n">
         <v>150</v>
       </c>
+      <c r="AU27" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -37553,6 +37631,9 @@
       <c r="AT28" t="n">
         <v>150</v>
       </c>
+      <c r="AU28" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -37678,6 +37759,9 @@
       <c r="AT29" t="n">
         <v>150</v>
       </c>
+      <c r="AU29" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -37803,6 +37887,9 @@
       <c r="AT30" t="n">
         <v>150</v>
       </c>
+      <c r="AU30" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -37983,6 +38070,9 @@
       <c r="AT32" t="n">
         <v>150</v>
       </c>
+      <c r="AU32" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -38119,6 +38209,9 @@
       <c r="AT33" t="n">
         <v>150</v>
       </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -38251,6 +38344,9 @@
       </c>
       <c r="AT34" t="n">
         <v>150</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -44812,6 +44908,1271 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>球员</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>睡眠(1-5)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>疲劳(1-5)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>酸痛(1-5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>训练内容</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RPE(0-10)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>时长(min)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sRPE</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>恢复建议</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张海轩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>脚踝痛</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>杨卓燠</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J3" t="n">
+        <v>200</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>腰疼</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王款(U21)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" t="n">
+        <v>150</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J5" t="n">
+        <v>300</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>略不舒服</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>150</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>凌中阳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J7" t="n">
+        <v>300</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>陈少豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>50</v>
+      </c>
+      <c r="J8" t="n">
+        <v>250</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>李金羽</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="n">
+        <v>250</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>王捷(U21)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+      <c r="J10" t="n">
+        <v>200</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>左膝</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>王皓文(U21)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J11" t="n">
+        <v>250</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>丁云峰</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" t="n">
+        <v>200</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J13" t="n">
+        <v>200</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>何麟立</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>250</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>布格拉汗-斯坎旦尔</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>200</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>巫林峰</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>200</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>栾昊(U21)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>50</v>
+      </c>
+      <c r="J19" t="n">
+        <v>50</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>陈祥煜</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" t="n">
+        <v>200</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>艾沙江-库尔班</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>50</v>
+      </c>
+      <c r="J21" t="n">
+        <v>250</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>帕尔曼江-克尤木</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>50</v>
+      </c>
+      <c r="J22" t="n">
+        <v>250</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>阿西江-白山</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" t="n">
+        <v>200</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MD-1踩场·热身5'+抢圈6'×2组+冲刺4次(2')+两人传球3'+战术演练15'+传中射门·50'</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>50</v>
+      </c>
+      <c r="J24" t="n">
+        <v>250</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>张辉</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>黄牌停赛·未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>谢锦政</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>林楷轩(U21)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>朱云天(U21)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>未跟队</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>未随队</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -44819,7 +46180,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -45772,7 +47133,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="12.9807692307692" customWidth="1" min="1" max="1"/>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
@@ -46975,7 +48336,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="11.6923076923077" customWidth="1" min="2" max="2"/>
   </cols>
@@ -48117,7 +49478,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="15.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="20.1923076923077" customWidth="1" min="2" max="2"/>
@@ -49322,7 +50683,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="19.8653846153846" customWidth="1" min="1" max="1"/>
     <col width="14.4134615384615" customWidth="1" min="2" max="2"/>
@@ -50302,7 +51663,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/public/share/data/每日监控.xlsx
+++ b/public/share/data/每日监控.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19700" windowHeight="9840" tabRatio="600" firstSheet="32" activeTab="39" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19700" windowHeight="9840" tabRatio="600" firstSheet="32" activeTab="38" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06" sheetId="1" state="visible" r:id="rId1"/>
@@ -1379,6 +1379,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3189,15 +3190,6 @@
           <t>缺席</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>375</v>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>MCL恢复期</t>
@@ -3819,6 +3811,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -5052,17 +5045,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>缺席</t>
+          <t>力量训练·康复期(40min)</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J27" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -5175,6 +5168,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -6306,6 +6300,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -7611,6 +7606,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -8890,6 +8886,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -9585,8 +9582,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>缺席</t>
-        </is>
+          <t>力量训练·康复期(40min)</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>40</v>
+      </c>
+      <c r="J24" t="n">
+        <v>200</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -9756,6 +9762,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -12393,6 +12400,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -13953,6 +13961,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -15223,6 +15232,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -15257,6 +15267,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -16159,6 +16170,9 @@
       <c r="I22" t="n">
         <v>60</v>
       </c>
+      <c r="J22" t="n">
+        <v>180</v>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>MD-1 M2 | RPE未填写</t>
@@ -16200,6 +16214,9 @@
       </c>
       <c r="I23" t="n">
         <v>60</v>
+      </c>
+      <c r="J23" t="n">
+        <v>120</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -19166,6 +19183,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -20333,6 +20351,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -21403,6 +21422,7 @@
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -22705,6 +22725,7 @@
       </c>
       <c r="L32" s="7" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -23973,6 +23994,7 @@
       <c r="K32" s="7" t="inlineStr"/>
       <c r="L32" s="7" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
@@ -25422,6 +25444,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -26888,6 +26911,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -29663,6 +29687,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -35554,6 +35579,7 @@
         <v>172</v>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -36882,6 +36908,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -38188,6 +38215,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -40748,9 +40776,23 @@
       <c r="F30" t="n">
         <v>2</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>热身5'+抢圈6'×2组+两人传球3'+战术演练30'·50'</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>50</v>
+      </c>
+      <c r="J30" t="n">
+        <v>150</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>脚崴缺席 脚踝疼</t>
+          <t>脚踝疼</t>
         </is>
       </c>
     </row>
@@ -42239,13 +42281,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2010</v>
+        <v>2160</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -42261,6 +42303,9 @@
       <c r="I4" t="n">
         <v>810</v>
       </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" t="n">
         <v>250</v>
       </c>
@@ -42270,6 +42315,9 @@
       <c r="M4" t="n">
         <v>300</v>
       </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
         <v>702</v>
       </c>
@@ -42279,12 +42327,18 @@
       <c r="Q4" t="n">
         <v>205</v>
       </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="n">
         <v>110</v>
       </c>
       <c r="T4" t="n">
         <v>760</v>
       </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
       <c r="V4" s="4" t="n">
         <v>840</v>
       </c>
@@ -42333,11 +42387,14 @@
       <c r="AM4" t="n">
         <v>950</v>
       </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
       <c r="AO4" t="n">
         <v>188</v>
       </c>
       <c r="AP4" t="n">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="AQ4" t="n">
         <v>760</v>
@@ -42349,7 +42406,7 @@
         <v>100</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AU4" t="n">
         <v>250</v>
@@ -42373,7 +42430,7 @@
         <v>725</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E5" t="n">
         <v>0.48</v>
@@ -42392,6 +42449,9 @@
       <c r="I5" t="n">
         <v>60</v>
       </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="n">
         <v>200</v>
       </c>
@@ -42401,6 +42461,9 @@
       <c r="M5" t="n">
         <v>240</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
       <c r="O5" t="n">
         <v>624</v>
       </c>
@@ -42410,12 +42473,18 @@
       <c r="Q5" t="n">
         <v>205</v>
       </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
       <c r="S5" t="n">
         <v>110</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
       <c r="V5" s="4" t="n">
         <v>770</v>
       </c>
@@ -42459,7 +42528,7 @@
         <v>152</v>
       </c>
       <c r="AM5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>196</v>
@@ -42468,7 +42537,7 @@
         <v>141</v>
       </c>
       <c r="AP5" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ5" t="n">
         <v>60</v>
@@ -42504,7 +42573,7 @@
         <v>675</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E6" t="n">
         <v>0.6</v>
@@ -42523,6 +42592,9 @@
       <c r="I6" t="n">
         <v>50</v>
       </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" t="n">
         <v>150</v>
       </c>
@@ -42532,6 +42604,9 @@
       <c r="M6" t="n">
         <v>180</v>
       </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
       <c r="O6" t="n">
         <v>390</v>
       </c>
@@ -42541,12 +42616,18 @@
       <c r="Q6" t="n">
         <v>205</v>
       </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" t="n">
         <v>110</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
       <c r="V6" s="4" t="n">
         <v>770</v>
       </c>
@@ -42593,7 +42674,7 @@
         <v>114</v>
       </c>
       <c r="AM6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>196</v>
@@ -42602,7 +42683,7 @@
         <v>94</v>
       </c>
       <c r="AP6" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AQ6" t="n">
         <v>60</v>
@@ -42638,10 +42719,10 @@
         <v>2630</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -42657,6 +42738,9 @@
       <c r="I7" t="n">
         <v>810</v>
       </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" t="n">
         <v>300</v>
       </c>
@@ -42666,6 +42750,9 @@
       <c r="M7" t="n">
         <v>240</v>
       </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
       <c r="O7" t="n">
         <v>468</v>
       </c>
@@ -42675,12 +42762,18 @@
       <c r="Q7" t="n">
         <v>246</v>
       </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
       <c r="S7" t="n">
         <v>330</v>
       </c>
       <c r="T7" t="n">
         <v>950</v>
       </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
       <c r="V7" s="4" t="n">
         <v>780</v>
       </c>
@@ -42729,11 +42822,14 @@
       <c r="AM7" t="n">
         <v>920</v>
       </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
       <c r="AO7" t="n">
         <v>141</v>
       </c>
       <c r="AP7" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ7" t="n">
         <v>950</v>
@@ -42769,10 +42865,10 @@
         <v>2100</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -42788,6 +42884,9 @@
       <c r="I8" t="n">
         <v>774</v>
       </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" t="n">
         <v>350</v>
       </c>
@@ -42797,6 +42896,9 @@
       <c r="M8" t="n">
         <v>180</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
       <c r="O8" t="n">
         <v>390</v>
       </c>
@@ -42806,12 +42908,18 @@
       <c r="Q8" t="n">
         <v>246</v>
       </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
       <c r="S8" t="n">
         <v>220</v>
       </c>
       <c r="T8" t="n">
         <v>665</v>
       </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
       <c r="V8" s="4" t="n">
         <v>710</v>
       </c>
@@ -42860,11 +42968,14 @@
       <c r="AM8" t="n">
         <v>665</v>
       </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
       <c r="AO8" t="n">
         <v>141</v>
       </c>
       <c r="AP8" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ8" t="n">
         <v>760</v>
@@ -42900,10 +43011,10 @@
         <v>1277</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E9" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -42919,6 +43030,21 @@
       <c r="I9" t="n">
         <v>711</v>
       </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" t="n">
         <v>468</v>
       </c>
@@ -42928,6 +43054,18 @@
       <c r="Q9" t="n">
         <v>246</v>
       </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
       <c r="V9" s="4" t="n">
         <v>770</v>
       </c>
@@ -42983,7 +43121,7 @@
         <v>141</v>
       </c>
       <c r="AP9" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ9" t="n">
         <v>66</v>
@@ -43038,6 +43176,9 @@
       <c r="I10" t="n">
         <v>70</v>
       </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
       <c r="K10" t="n">
         <v>150</v>
       </c>
@@ -43047,6 +43188,9 @@
       <c r="M10" t="n">
         <v>180</v>
       </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
       <c r="O10" t="n">
         <v>468</v>
       </c>
@@ -43056,12 +43200,18 @@
       <c r="Q10" t="n">
         <v>246</v>
       </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
       <c r="S10" t="n">
         <v>220</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
       <c r="V10" s="4" t="n">
         <v>700</v>
       </c>
@@ -43108,7 +43258,7 @@
         <v>114</v>
       </c>
       <c r="AM10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>224</v>
@@ -43117,7 +43267,7 @@
         <v>94</v>
       </c>
       <c r="AP10" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AQ10" t="n">
         <v>60</v>
@@ -43153,10 +43303,10 @@
         <v>655</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E11" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -43172,6 +43322,9 @@
       <c r="I11" t="n">
         <v>55</v>
       </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" t="n">
         <v>250</v>
       </c>
@@ -43181,6 +43334,9 @@
       <c r="M11" t="n">
         <v>180</v>
       </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
       <c r="O11" t="n">
         <v>390</v>
       </c>
@@ -43190,12 +43346,18 @@
       <c r="Q11" t="n">
         <v>246</v>
       </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
       <c r="S11" t="n">
         <v>275</v>
       </c>
       <c r="T11" t="n">
         <v>760</v>
       </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
       <c r="V11" s="4" t="n">
         <v>770</v>
       </c>
@@ -43251,11 +43413,14 @@
         <v>94</v>
       </c>
       <c r="AP11" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AQ11" t="n">
         <v>60</v>
       </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
       <c r="AS11" t="n">
         <v>150</v>
       </c>
@@ -43284,10 +43449,10 @@
         <v>770</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E12" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -43303,6 +43468,9 @@
       <c r="I12" t="n">
         <v>729</v>
       </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
       <c r="K12" t="n">
         <v>300</v>
       </c>
@@ -43312,6 +43480,9 @@
       <c r="M12" t="n">
         <v>240</v>
       </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
       <c r="O12" t="n">
         <v>468</v>
       </c>
@@ -43321,12 +43492,18 @@
       <c r="Q12" t="n">
         <v>164</v>
       </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
       <c r="S12" t="n">
         <v>220</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
       <c r="V12" s="4" t="n">
         <v>710</v>
       </c>
@@ -43343,7 +43520,7 @@
         <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD12" t="n">
         <v>240</v>
@@ -43382,7 +43559,7 @@
         <v>141</v>
       </c>
       <c r="AP12" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AQ12" t="n">
         <v>45</v>
@@ -43418,10 +43595,10 @@
         <v>2310</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E13" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -43437,6 +43614,9 @@
       <c r="I13" t="n">
         <v>900</v>
       </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
       <c r="K13" t="n">
         <v>250</v>
       </c>
@@ -43446,6 +43626,9 @@
       <c r="M13" t="n">
         <v>240</v>
       </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
       <c r="O13" t="n">
         <v>468</v>
       </c>
@@ -43455,12 +43638,18 @@
       <c r="Q13" t="n">
         <v>246</v>
       </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
       <c r="S13" t="n">
         <v>275</v>
       </c>
       <c r="T13" t="n">
         <v>855</v>
       </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" s="4" t="n">
         <v>770</v>
       </c>
@@ -43509,11 +43698,14 @@
       <c r="AM13" t="n">
         <v>855</v>
       </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
       <c r="AO13" t="n">
         <v>188</v>
       </c>
       <c r="AP13" t="n">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="AQ13" t="n">
         <v>760</v>
@@ -43549,10 +43741,10 @@
         <v>2255</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -43565,6 +43757,21 @@
       <c r="H14" t="n">
         <v>180</v>
       </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
       <c r="O14" t="n">
         <v>312</v>
       </c>
@@ -43574,6 +43781,18 @@
       <c r="Q14" t="n">
         <v>205</v>
       </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" s="4" t="n">
         <v>700</v>
       </c>
@@ -43622,11 +43841,14 @@
       <c r="AM14" t="n">
         <v>855</v>
       </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
       <c r="AO14" t="n">
         <v>141</v>
       </c>
       <c r="AP14" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ14" t="n">
         <v>855</v>
@@ -43662,10 +43884,10 @@
         <v>735</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E15" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -43675,12 +43897,27 @@
       <c r="G15" t="n">
         <v>225</v>
       </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" t="n">
         <v>70</v>
       </c>
       <c r="M15" t="n">
         <v>240</v>
       </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
       <c r="O15" t="n">
         <v>468</v>
       </c>
@@ -43690,12 +43927,18 @@
       <c r="Q15" t="n">
         <v>246</v>
       </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
       <c r="S15" t="n">
         <v>330</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" s="4" t="n">
         <v>710</v>
       </c>
@@ -43741,6 +43984,9 @@
       <c r="AL15" t="n">
         <v>152</v>
       </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
       <c r="AN15" t="n">
         <v>196</v>
       </c>
@@ -43748,7 +43994,7 @@
         <v>141</v>
       </c>
       <c r="AP15" t="n">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="AQ15" t="n">
         <v>45</v>
@@ -43794,6 +44040,30 @@
           <t>🟢 低负荷</t>
         </is>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" s="4" t="n">
         <v>700</v>
       </c>
@@ -43836,6 +44106,18 @@
       <c r="AK16" t="n">
         <v>36</v>
       </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
@@ -43873,10 +44155,10 @@
         <v>2153</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -43892,6 +44174,9 @@
       <c r="I17" t="n">
         <v>102</v>
       </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" t="n">
         <v>250</v>
       </c>
@@ -43901,6 +44186,9 @@
       <c r="M17" t="n">
         <v>300</v>
       </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
       <c r="O17" t="n">
         <v>624</v>
       </c>
@@ -43910,12 +44198,18 @@
       <c r="Q17" t="n">
         <v>246</v>
       </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
       <c r="S17" t="n">
         <v>220</v>
       </c>
       <c r="T17" t="n">
         <v>483</v>
       </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
       <c r="V17" s="4" t="n">
         <v>700</v>
       </c>
@@ -43964,11 +44258,14 @@
       <c r="AM17" t="n">
         <v>950</v>
       </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
       <c r="AO17" t="n">
         <v>141</v>
       </c>
       <c r="AP17" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ17" t="n">
         <v>672</v>
@@ -44004,10 +44301,10 @@
         <v>1508</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E18" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -44023,6 +44320,9 @@
       <c r="I18" t="n">
         <v>790</v>
       </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
       <c r="K18" t="n">
         <v>200</v>
       </c>
@@ -44032,6 +44332,9 @@
       <c r="M18" t="n">
         <v>180</v>
       </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
       <c r="O18" t="n">
         <v>468</v>
       </c>
@@ -44041,12 +44344,18 @@
       <c r="Q18" t="n">
         <v>287</v>
       </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
       <c r="S18" t="n">
         <v>220</v>
       </c>
       <c r="T18" t="n">
         <v>483</v>
       </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
       <c r="V18" s="4" t="n">
         <v>700</v>
       </c>
@@ -44095,11 +44404,14 @@
       <c r="AM18" t="n">
         <v>568</v>
       </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
       <c r="AO18" t="n">
         <v>188</v>
       </c>
       <c r="AP18" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ18" t="n">
         <v>440</v>
@@ -44135,10 +44447,10 @@
         <v>1280</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -44154,6 +44466,9 @@
       <c r="I19" t="n">
         <v>900</v>
       </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
       <c r="K19" t="n">
         <v>200</v>
       </c>
@@ -44163,6 +44478,9 @@
       <c r="M19" t="n">
         <v>240</v>
       </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
       <c r="O19" t="n">
         <v>468</v>
       </c>
@@ -44172,12 +44490,18 @@
       <c r="Q19" t="n">
         <v>287</v>
       </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
       <c r="S19" t="n">
         <v>220</v>
       </c>
       <c r="T19" t="n">
         <v>950</v>
       </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
       <c r="V19" s="4" t="n">
         <v>700</v>
       </c>
@@ -44226,11 +44550,14 @@
       <c r="AM19" t="n">
         <v>860</v>
       </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
       <c r="AO19" t="n">
         <v>141</v>
       </c>
       <c r="AP19" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ19" t="n">
         <v>760</v>
@@ -44266,7 +44593,7 @@
         <v>100</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E20" t="n">
         <v>0.07000000000000001</v>
@@ -44285,6 +44612,9 @@
       <c r="I20" t="n">
         <v>40</v>
       </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
       <c r="K20" t="n">
         <v>150</v>
       </c>
@@ -44294,6 +44624,9 @@
       <c r="M20" t="n">
         <v>120</v>
       </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
       <c r="O20" t="n">
         <v>468</v>
       </c>
@@ -44303,12 +44636,18 @@
       <c r="Q20" t="n">
         <v>246</v>
       </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
       <c r="S20" t="n">
         <v>220</v>
       </c>
       <c r="T20" t="n">
         <v>75</v>
       </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
       <c r="V20" s="4" t="n">
         <v>640</v>
       </c>
@@ -44355,7 +44694,13 @@
         <v>114</v>
       </c>
       <c r="AM20" t="n">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -44363,6 +44708,9 @@
       <c r="AQ20" t="n">
         <v>0</v>
       </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
@@ -44391,10 +44739,10 @@
         <v>745</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E21" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -44410,6 +44758,9 @@
       <c r="I21" t="n">
         <v>50</v>
       </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
       <c r="K21" t="n">
         <v>150</v>
       </c>
@@ -44419,6 +44770,9 @@
       <c r="M21" t="n">
         <v>120</v>
       </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
       <c r="O21" t="n">
         <v>468</v>
       </c>
@@ -44428,12 +44782,18 @@
       <c r="Q21" t="n">
         <v>205</v>
       </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
       <c r="S21" t="n">
         <v>165</v>
       </c>
       <c r="T21" t="n">
         <v>30</v>
       </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
       <c r="V21" s="4" t="n">
         <v>640</v>
       </c>
@@ -44480,7 +44840,7 @@
         <v>114</v>
       </c>
       <c r="AM21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
         <v>196</v>
@@ -44489,7 +44849,7 @@
         <v>188</v>
       </c>
       <c r="AP21" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ21" t="n">
         <v>45</v>
@@ -44544,6 +44904,9 @@
       <c r="I22" t="n">
         <v>50</v>
       </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
       <c r="K22" t="n">
         <v>150</v>
       </c>
@@ -44553,6 +44916,9 @@
       <c r="M22" t="n">
         <v>120</v>
       </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
       <c r="O22" t="n">
         <v>390</v>
       </c>
@@ -44562,12 +44928,18 @@
       <c r="Q22" t="n">
         <v>246</v>
       </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
       <c r="S22" t="n">
         <v>220</v>
       </c>
       <c r="T22" t="n">
         <v>75</v>
       </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
       <c r="V22" s="4" t="n">
         <v>700</v>
       </c>
@@ -44614,7 +44986,7 @@
         <v>114</v>
       </c>
       <c r="AM22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
         <v>196</v>
@@ -44623,7 +44995,7 @@
         <v>141</v>
       </c>
       <c r="AP22" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AQ22" t="n">
         <v>45</v>
@@ -44659,10 +45031,10 @@
         <v>320</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E23" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -44672,6 +45044,15 @@
       <c r="G23" t="n">
         <v>225</v>
       </c>
+      <c r="H23" t="n">
+        <v>120</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
       <c r="K23" t="n">
         <v>100</v>
       </c>
@@ -44681,6 +45062,9 @@
       <c r="M23" t="n">
         <v>120</v>
       </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
       <c r="O23" t="n">
         <v>468</v>
       </c>
@@ -44690,12 +45074,18 @@
       <c r="Q23" t="n">
         <v>105</v>
       </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
       <c r="S23" t="n">
         <v>165</v>
       </c>
       <c r="T23" t="n">
         <v>25</v>
       </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
       <c r="V23" s="4" t="n">
         <v>700</v>
       </c>
@@ -44738,12 +45128,18 @@
       <c r="AK23" t="n">
         <v>72</v>
       </c>
+      <c r="AL23" t="n">
+        <v>114</v>
+      </c>
       <c r="AM23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
         <v>196</v>
       </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
       <c r="AP23" t="n">
         <v>0</v>
       </c>
@@ -44794,12 +45190,27 @@
       <c r="G24" t="n">
         <v>225</v>
       </c>
+      <c r="H24" t="n">
+        <v>180</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" t="n">
         <v>70</v>
       </c>
       <c r="M24" t="n">
         <v>240</v>
       </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
       <c r="O24" t="n">
         <v>390</v>
       </c>
@@ -44809,6 +45220,18 @@
       <c r="Q24" t="n">
         <v>15</v>
       </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
       <c r="V24" s="4" t="n">
         <v>700</v>
       </c>
@@ -44851,6 +45274,18 @@
       <c r="AK24" t="n">
         <v>180</v>
       </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
       <c r="AP24" t="n">
         <v>0</v>
       </c>
@@ -44898,6 +45333,24 @@
           <t>🟢 低负荷</t>
         </is>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
       <c r="V25" s="4" t="n">
         <v>780</v>
       </c>
@@ -44937,12 +45390,27 @@
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
       <c r="AP25" t="n">
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
       </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
       <c r="AS25" t="n">
         <v>0</v>
       </c>
@@ -44971,15 +45439,57 @@
         <v>904</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E26" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>🟢 安全</t>
         </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>200</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>200</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>200</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>570</v>
@@ -45027,7 +45537,7 @@
         <v>114</v>
       </c>
       <c r="AM26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
         <v>196</v>
@@ -45036,7 +45546,7 @@
         <v>94</v>
       </c>
       <c r="AP26" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AQ26" t="n">
         <v>45</v>
@@ -45072,10 +45582,10 @@
         <v>2285</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -45091,6 +45601,9 @@
       <c r="I27" t="n">
         <v>900</v>
       </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
       <c r="K27" t="n">
         <v>150</v>
       </c>
@@ -45100,6 +45613,9 @@
       <c r="M27" t="n">
         <v>180</v>
       </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
       <c r="O27" t="n">
         <v>390</v>
       </c>
@@ -45109,12 +45625,18 @@
       <c r="Q27" t="n">
         <v>164</v>
       </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
       <c r="S27" t="n">
         <v>165</v>
       </c>
       <c r="T27" t="n">
         <v>765</v>
       </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
       <c r="V27" s="4" t="n">
         <v>640</v>
       </c>
@@ -45163,11 +45685,14 @@
       <c r="AM27" t="n">
         <v>950</v>
       </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
       <c r="AO27" t="n">
         <v>235</v>
       </c>
       <c r="AP27" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ27" t="n">
         <v>855</v>
@@ -45203,10 +45728,10 @@
         <v>2710</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E28" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -45222,6 +45747,9 @@
       <c r="I28" t="n">
         <v>900</v>
       </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
       <c r="K28" t="n">
         <v>350</v>
       </c>
@@ -45231,6 +45759,9 @@
       <c r="M28" t="n">
         <v>180</v>
       </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
       <c r="O28" t="n">
         <v>546</v>
       </c>
@@ -45240,12 +45771,18 @@
       <c r="Q28" t="n">
         <v>287</v>
       </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
       <c r="S28" t="n">
         <v>165</v>
       </c>
       <c r="T28" t="n">
         <v>950</v>
       </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
       <c r="V28" s="4" t="n">
         <v>710</v>
       </c>
@@ -45294,11 +45831,14 @@
       <c r="AM28" t="n">
         <v>920</v>
       </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
       <c r="AO28" t="n">
         <v>188</v>
       </c>
       <c r="AP28" t="n">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="AQ28" t="n">
         <v>950</v>
@@ -45334,10 +45874,10 @@
         <v>2535</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -45353,6 +45893,9 @@
       <c r="I29" t="n">
         <v>900</v>
       </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
       <c r="K29" t="n">
         <v>350</v>
       </c>
@@ -45362,6 +45905,9 @@
       <c r="M29" t="n">
         <v>180</v>
       </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
       <c r="O29" t="n">
         <v>546</v>
       </c>
@@ -45371,12 +45917,18 @@
       <c r="Q29" t="n">
         <v>287</v>
       </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
       <c r="S29" t="n">
         <v>165</v>
       </c>
       <c r="T29" t="n">
         <v>950</v>
       </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
       <c r="V29" s="4" t="n">
         <v>840</v>
       </c>
@@ -45425,11 +45977,14 @@
       <c r="AM29" t="n">
         <v>950</v>
       </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
       <c r="AO29" t="n">
         <v>235</v>
       </c>
       <c r="AP29" t="n">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c r="AQ29" t="n">
         <v>855</v>
@@ -45465,10 +46020,10 @@
         <v>1288</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E30" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -45484,6 +46039,9 @@
       <c r="I30" t="n">
         <v>112</v>
       </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
       <c r="K30" t="n">
         <v>100</v>
       </c>
@@ -45493,6 +46051,9 @@
       <c r="M30" t="n">
         <v>120</v>
       </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
       <c r="O30" t="n">
         <v>546</v>
       </c>
@@ -45502,12 +46063,18 @@
       <c r="Q30" t="n">
         <v>164</v>
       </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
       <c r="S30" t="n">
         <v>165</v>
       </c>
       <c r="T30" t="n">
         <v>208</v>
       </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
       <c r="V30" s="4" t="n">
         <v>640</v>
       </c>
@@ -45553,6 +46120,9 @@
       <c r="AL30" t="n">
         <v>152</v>
       </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
       <c r="AN30" t="n">
         <v>196</v>
       </c>
@@ -45560,7 +46130,7 @@
         <v>94</v>
       </c>
       <c r="AP30" t="n">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="AQ30" t="n">
         <v>320</v>
@@ -45615,6 +46185,9 @@
       <c r="I31" t="n">
         <v>50</v>
       </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
       <c r="K31" t="n">
         <v>100</v>
       </c>
@@ -45624,6 +46197,9 @@
       <c r="M31" t="n">
         <v>60</v>
       </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
       <c r="O31" t="n">
         <v>390</v>
       </c>
@@ -45633,6 +46209,18 @@
       <c r="Q31" t="n">
         <v>63</v>
       </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
@@ -45673,15 +46261,21 @@
         <v>928</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E32" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>🟢 低负荷</t>
         </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>110</v>
@@ -45689,6 +46283,9 @@
       <c r="T32" t="n">
         <v>182</v>
       </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
       <c r="V32" s="4" t="n">
         <v>700</v>
       </c>
@@ -45744,7 +46341,7 @@
         <v>235</v>
       </c>
       <c r="AP32" t="n">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="AQ32" t="n">
         <v>60</v>
@@ -45780,10 +46377,10 @@
         <v>430</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E33" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -45839,7 +46436,7 @@
         <v>500</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -45883,6 +46480,18 @@
       <c r="AK33" t="n">
         <v>108</v>
       </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
       <c r="AP33" t="n">
         <v>0</v>
       </c>
@@ -45920,14 +46529,14 @@
         <v>585</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E34" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>🟠 注意</t>
+          <t>🟢 安全</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -45979,7 +46588,7 @@
         <v>510</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X34" t="n">
         <v>100</v>
@@ -46020,6 +46629,18 @@
       <c r="AK34" t="n">
         <v>72</v>
       </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
       <c r="AP34" t="n">
         <v>0</v>
       </c>
@@ -46119,6 +46740,9 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0</v>
       </c>
       <c r="AA35" t="n">
@@ -46197,6 +46821,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -47138,7 +47763,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -48486,6 +49111,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -48518,6 +49144,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -49720,6 +50347,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -53771,17 +54399,17 @@
       <c r="F16" s="20" t="inlineStr"/>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>缺席</t>
+          <t>力量训练·康复期(40min)</t>
         </is>
       </c>
       <c r="H16" s="22" t="n">
         <v>5</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="K16" s="20" t="inlineStr"/>
       <c r="L16" s="23" t="inlineStr"/>
